--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_oil_gas_production_and_exploration.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="tsxv_tpl" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,34 +590,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0363</v>
+        <v>0.492</v>
       </c>
       <c r="G2">
-        <v>0.4175182481751824</v>
+        <v>0.1652951699463328</v>
       </c>
       <c r="H2">
-        <v>0.4175182481751824</v>
+        <v>0.1652951699463328</v>
       </c>
       <c r="I2">
-        <v>-1.774087591240876</v>
+        <v>0.6493738819320214</v>
       </c>
       <c r="J2">
-        <v>-1.774087591240876</v>
+        <v>0.3327816292449417</v>
       </c>
       <c r="K2">
-        <v>-45.8</v>
+        <v>18.5</v>
       </c>
       <c r="L2">
-        <v>-1.671532846715329</v>
+        <v>0.3309481216457961</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.592</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.009411764705882352</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.032</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +626,82 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.592</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>1.888</v>
+        <v>15</v>
       </c>
       <c r="V2">
-        <v>0.01838364167478091</v>
+        <v>0.2384737678855326</v>
       </c>
       <c r="W2">
-        <v>-0.457777935337493</v>
+        <v>0.7283464566929134</v>
       </c>
       <c r="X2">
-        <v>0.09088526771279032</v>
+        <v>0.1266026933997386</v>
       </c>
       <c r="Y2">
-        <v>-0.5486632030502834</v>
+        <v>0.6017437632931748</v>
       </c>
       <c r="Z2">
-        <v>0.2358977891039328</v>
+        <v>1.800786031827846</v>
       </c>
       <c r="AA2">
-        <v>-0.4014110256468706</v>
+        <v>0.5992685095932042</v>
       </c>
       <c r="AB2">
-        <v>0.07619791249143237</v>
+        <v>0.1231774053520593</v>
       </c>
       <c r="AC2">
-        <v>-0.477608938138303</v>
+        <v>0.4760911042411449</v>
       </c>
       <c r="AD2">
-        <v>33.1</v>
+        <v>4.71</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>33.1</v>
+        <v>4.71</v>
       </c>
       <c r="AG2">
-        <v>31.212</v>
+        <v>-10.29</v>
       </c>
       <c r="AH2">
-        <v>0.243740795287187</v>
+        <v>0.0696642508504659</v>
       </c>
       <c r="AI2">
-        <v>0.4041514041514042</v>
+        <v>0.09790064435668261</v>
       </c>
       <c r="AJ2">
-        <v>0.2330784395722564</v>
+        <v>-0.1955901919787112</v>
       </c>
       <c r="AK2">
-        <v>0.3900914862770585</v>
+        <v>-0.3107822410147991</v>
       </c>
       <c r="AL2">
-        <v>2.3</v>
+        <v>0.975</v>
       </c>
       <c r="AM2">
-        <v>2.156</v>
+        <v>0.948</v>
       </c>
       <c r="AN2">
-        <v>2.833904109589041</v>
+        <v>0.1035164835164835</v>
       </c>
       <c r="AO2">
-        <v>-21.13478260869566</v>
+        <v>37.23076923076923</v>
       </c>
       <c r="AP2">
-        <v>2.672260273972603</v>
+        <v>-0.2261538461538461</v>
       </c>
       <c r="AQ2">
-        <v>-22.54638218923933</v>
+        <v>38.29113924050633</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +712,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zoltav Resources Inc. (AIM:ZOL)</t>
+          <t>Tethys Petroleum Limited (TSXV:TPL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,34 +721,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0341</v>
+        <v>0.492</v>
       </c>
       <c r="G3">
-        <v>0.2652173913043478</v>
+        <v>0.1652951699463328</v>
       </c>
       <c r="H3">
-        <v>0.2652173913043478</v>
+        <v>0.1652951699463328</v>
       </c>
       <c r="I3">
-        <v>-0.5720496894409938</v>
+        <v>0.6493738819320214</v>
       </c>
       <c r="J3">
-        <v>-0.5720496894409938</v>
+        <v>0.3327816292449417</v>
       </c>
       <c r="K3">
-        <v>-10.1</v>
+        <v>18.5</v>
       </c>
       <c r="L3">
-        <v>-0.6273291925465838</v>
+        <v>0.3309481216457961</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.592</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.009411764705882352</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,207 +757,8794 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.592</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>1.23</v>
+        <v>15</v>
       </c>
       <c r="V3">
-        <v>0.02847222222222222</v>
+        <v>0.2384737678855326</v>
       </c>
       <c r="W3">
-        <v>-0.2936046511627907</v>
+        <v>0.7283464566929134</v>
       </c>
       <c r="X3">
-        <v>0.1051871744298363</v>
+        <v>0.1266026933997386</v>
       </c>
       <c r="Y3">
-        <v>-0.398791825592627</v>
+        <v>0.6017437632931748</v>
       </c>
       <c r="Z3">
-        <v>0.2994680257430899</v>
+        <v>1.800786031827846</v>
       </c>
       <c r="AA3">
-        <v>-0.1713105911238421</v>
+        <v>0.5992685095932042</v>
       </c>
       <c r="AB3">
-        <v>0.0775907444480146</v>
+        <v>0.1231774053520593</v>
       </c>
       <c r="AC3">
-        <v>-0.2489013355718567</v>
+        <v>0.4760911042411449</v>
       </c>
       <c r="AD3">
-        <v>26.8</v>
+        <v>4.71</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>26.8</v>
+        <v>4.71</v>
       </c>
       <c r="AG3">
-        <v>25.57</v>
+        <v>-10.29</v>
       </c>
       <c r="AH3">
-        <v>0.3828571428571428</v>
+        <v>0.0696642508504659</v>
       </c>
       <c r="AI3">
-        <v>0.5338645418326693</v>
+        <v>0.09790064435668261</v>
       </c>
       <c r="AJ3">
-        <v>0.3718191071688235</v>
+        <v>-0.1955901919787112</v>
       </c>
       <c r="AK3">
-        <v>0.522156422299367</v>
+        <v>-0.3107822410147991</v>
       </c>
       <c r="AL3">
+        <v>0.975</v>
+      </c>
+      <c r="AM3">
+        <v>0.948</v>
+      </c>
+      <c r="AN3">
+        <v>0.1035164835164835</v>
+      </c>
+      <c r="AO3">
+        <v>37.23076923076923</v>
+      </c>
+      <c r="AP3">
+        <v>-0.2261538461538461</v>
+      </c>
+      <c r="AQ3">
+        <v>38.29113924050633</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tethys Petroleum Limited (TSXV:TPL)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TSXV:TPL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oil/Gas (Production and Exploration)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0696642508504659</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>62.9</v>
+      </c>
+      <c r="H2">
+        <v>67.96248001487351</v>
+      </c>
+      <c r="I2">
+        <v>52.61</v>
+      </c>
+      <c r="J2">
+        <v>52.9624800148735</v>
+      </c>
+      <c r="K2">
+        <v>4.71</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0.123177405352059</v>
+      </c>
+      <c r="N2">
+        <v>0.120485984541393</v>
+      </c>
+      <c r="O2">
+        <v>0.0774341743119266</v>
+      </c>
+      <c r="P2">
+        <v>0.0457</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.126602693399739</v>
+      </c>
+      <c r="T2">
+        <v>0.120485984541393</v>
+      </c>
+      <c r="U2">
+        <v>1.26356318840793</v>
+      </c>
+      <c r="V2">
+        <v>1.17553800548526</v>
+      </c>
+      <c r="W2">
+        <v>10000000</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>62.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.06948816980840411</v>
+      </c>
+      <c r="AC2">
+        <v>0.07743417431192662</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>45.5</v>
+      </c>
+      <c r="AH2">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="AI2">
+        <v>15.9</v>
+      </c>
+      <c r="AJ2">
+        <v>4.71</v>
+      </c>
+      <c r="AK2">
+        <v>4.71</v>
+      </c>
+      <c r="AL2">
+        <v>0.975</v>
+      </c>
+      <c r="AM2">
+        <v>4.71</v>
+      </c>
+      <c r="AN2">
+        <v>15</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1204859845413926</v>
+      </c>
+      <c r="C2">
+        <v>67.96248001487352</v>
+      </c>
+      <c r="D2">
+        <v>52.96248001487352</v>
+      </c>
+      <c r="E2">
+        <v>-4.71</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>15</v>
+      </c>
+      <c r="H2">
+        <v>62.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>45.5</v>
+      </c>
+      <c r="K2">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L2">
+        <v>36.28</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>36.28</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>36.28</v>
+      </c>
+      <c r="Q2">
+        <v>45.5</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1204859845413926</v>
+      </c>
+      <c r="T2">
+        <v>1.175538005485263</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0.0457</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1205549845413926</v>
+      </c>
+      <c r="C3">
+        <v>67.27728449757772</v>
+      </c>
+      <c r="D3">
+        <v>52.95338449757773</v>
+      </c>
+      <c r="E3">
+        <v>-4.0339</v>
+      </c>
+      <c r="F3">
+        <v>0.6761</v>
+      </c>
+      <c r="G3">
+        <v>15</v>
+      </c>
+      <c r="H3">
+        <v>62.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>45.5</v>
+      </c>
+      <c r="K3">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L3">
+        <v>36.28</v>
+      </c>
+      <c r="M3">
+        <v>0.03089777</v>
+      </c>
+      <c r="N3">
+        <v>36.24910223</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>36.24910223</v>
+      </c>
+      <c r="Q3">
+        <v>45.46910223</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1213110954963562</v>
+      </c>
+      <c r="T3">
+        <v>1.187412126752791</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0.0457</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>1174.194771985162</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1206239845413926</v>
+      </c>
+      <c r="C4">
+        <v>66.59209210378485</v>
+      </c>
+      <c r="D4">
+        <v>52.94429210378484</v>
+      </c>
+      <c r="E4">
+        <v>-3.3578</v>
+      </c>
+      <c r="F4">
+        <v>1.3522</v>
+      </c>
+      <c r="G4">
+        <v>15</v>
+      </c>
+      <c r="H4">
+        <v>62.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>45.5</v>
+      </c>
+      <c r="K4">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L4">
+        <v>36.28</v>
+      </c>
+      <c r="M4">
+        <v>0.06179554000000001</v>
+      </c>
+      <c r="N4">
+        <v>36.21820446</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>36.21820446</v>
+      </c>
+      <c r="Q4">
+        <v>45.43820446</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1221530454504007</v>
+      </c>
+      <c r="T4">
+        <v>1.199528577025779</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0.0457</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>587.0973859925813</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1206929845413926</v>
+      </c>
+      <c r="C5">
+        <v>65.90690283188616</v>
+      </c>
+      <c r="D5">
+        <v>52.93520283188616</v>
+      </c>
+      <c r="E5">
+        <v>-2.6817</v>
+      </c>
+      <c r="F5">
+        <v>2.0283</v>
+      </c>
+      <c r="G5">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>62.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>45.5</v>
+      </c>
+      <c r="K5">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L5">
+        <v>36.28</v>
+      </c>
+      <c r="M5">
+        <v>0.09269331</v>
+      </c>
+      <c r="N5">
+        <v>36.18730669</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>36.18730669</v>
+      </c>
+      <c r="Q5">
+        <v>45.40730669</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.123012355197312</v>
+      </c>
+      <c r="T5">
+        <v>1.211894851015735</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0.0457</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>391.3982573283876</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1207619845413926</v>
+      </c>
+      <c r="C6">
+        <v>65.22171668027407</v>
+      </c>
+      <c r="D6">
+        <v>52.92611668027408</v>
+      </c>
+      <c r="E6">
+        <v>-2.0056</v>
+      </c>
+      <c r="F6">
+        <v>2.7044</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>62.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>45.5</v>
+      </c>
+      <c r="K6">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L6">
+        <v>36.28</v>
+      </c>
+      <c r="M6">
+        <v>0.12359108</v>
+      </c>
+      <c r="N6">
+        <v>36.15640892</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>36.15640892</v>
+      </c>
+      <c r="Q6">
+        <v>45.37640892</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1238895672306173</v>
+      </c>
+      <c r="T6">
+        <v>1.224518755713816</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0.0457</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>293.5486929962906</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1208309845413926</v>
+      </c>
+      <c r="C7">
+        <v>64.53653364734215</v>
+      </c>
+      <c r="D7">
+        <v>52.91703364734215</v>
+      </c>
+      <c r="E7">
+        <v>-1.3295</v>
+      </c>
+      <c r="F7">
+        <v>3.3805</v>
+      </c>
+      <c r="G7">
+        <v>15</v>
+      </c>
+      <c r="H7">
+        <v>62.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>45.5</v>
+      </c>
+      <c r="K7">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L7">
+        <v>36.28</v>
+      </c>
+      <c r="M7">
+        <v>0.15448885</v>
+      </c>
+      <c r="N7">
+        <v>36.12551115</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>36.12551115</v>
+      </c>
+      <c r="Q7">
+        <v>45.34551115</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1247852468856765</v>
+      </c>
+      <c r="T7">
+        <v>1.237408426826593</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0.0457</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>234.8389543970325</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1208999845413927</v>
+      </c>
+      <c r="C8">
+        <v>63.85135373148498</v>
+      </c>
+      <c r="D8">
+        <v>52.90795373148497</v>
+      </c>
+      <c r="E8">
+        <v>-0.6534000000000004</v>
+      </c>
+      <c r="F8">
+        <v>4.0566</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>62.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>45.5</v>
+      </c>
+      <c r="K8">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L8">
+        <v>36.28</v>
+      </c>
+      <c r="M8">
+        <v>0.18538662</v>
+      </c>
+      <c r="N8">
+        <v>36.09461338</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>36.09461338</v>
+      </c>
+      <c r="Q8">
+        <v>45.31461338</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.125699983554673</v>
+      </c>
+      <c r="T8">
+        <v>1.250572346260918</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0.0457</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>195.6991286641938</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1209689845413927</v>
+      </c>
+      <c r="C9">
+        <v>63.16617693109824</v>
+      </c>
+      <c r="D9">
+        <v>52.89887693109825</v>
+      </c>
+      <c r="E9">
+        <v>0.02270000000000039</v>
+      </c>
+      <c r="F9">
+        <v>4.7327</v>
+      </c>
+      <c r="G9">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>62.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>45.5</v>
+      </c>
+      <c r="K9">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L9">
+        <v>36.28</v>
+      </c>
+      <c r="M9">
+        <v>0.21628439</v>
+      </c>
+      <c r="N9">
+        <v>36.06371561</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>36.06371561</v>
+      </c>
+      <c r="Q9">
+        <v>45.28371561</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1266343919799921</v>
+      </c>
+      <c r="T9">
+        <v>1.264019360736842</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0.0457</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>167.7421102835947</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1210379845413927</v>
+      </c>
+      <c r="C10">
+        <v>62.48100324457884</v>
+      </c>
+      <c r="D10">
+        <v>52.88980324457884</v>
+      </c>
+      <c r="E10">
+        <v>0.6988000000000003</v>
+      </c>
+      <c r="F10">
+        <v>5.4088</v>
+      </c>
+      <c r="G10">
+        <v>15</v>
+      </c>
+      <c r="H10">
+        <v>62.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>45.5</v>
+      </c>
+      <c r="K10">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L10">
+        <v>36.28</v>
+      </c>
+      <c r="M10">
+        <v>0.24718216</v>
+      </c>
+      <c r="N10">
+        <v>36.03281784</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>36.03281784</v>
+      </c>
+      <c r="Q10">
+        <v>45.25281784</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1275891136319485</v>
+      </c>
+      <c r="T10">
+        <v>1.277758701614416</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0.0457</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>146.7743464981453</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1211069845413926</v>
+      </c>
+      <c r="C11">
+        <v>61.79583267032464</v>
+      </c>
+      <c r="D11">
+        <v>52.88073267032463</v>
+      </c>
+      <c r="E11">
+        <v>1.374899999999999</v>
+      </c>
+      <c r="F11">
+        <v>6.084899999999999</v>
+      </c>
+      <c r="G11">
+        <v>15</v>
+      </c>
+      <c r="H11">
+        <v>62.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>45.5</v>
+      </c>
+      <c r="K11">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L11">
+        <v>36.28</v>
+      </c>
+      <c r="M11">
+        <v>0.27807993</v>
+      </c>
+      <c r="N11">
+        <v>36.00192007</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>36.00192007</v>
+      </c>
+      <c r="Q11">
+        <v>45.22192007</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1285648181773545</v>
+      </c>
+      <c r="T11">
+        <v>1.291800006027762</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0.0457</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>130.4660857761292</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1211759845413927</v>
+      </c>
+      <c r="C12">
+        <v>61.11066520673466</v>
+      </c>
+      <c r="D12">
+        <v>52.87166520673465</v>
+      </c>
+      <c r="E12">
+        <v>2.051</v>
+      </c>
+      <c r="F12">
+        <v>6.761</v>
+      </c>
+      <c r="G12">
+        <v>15</v>
+      </c>
+      <c r="H12">
+        <v>62.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>45.5</v>
+      </c>
+      <c r="K12">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L12">
+        <v>36.28</v>
+      </c>
+      <c r="M12">
+        <v>0.3089777</v>
+      </c>
+      <c r="N12">
+        <v>35.9710223</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>35.9710223</v>
+      </c>
+      <c r="Q12">
+        <v>45.1910223</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1295622050459918</v>
+      </c>
+      <c r="T12">
+        <v>1.30615333942807</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0.0457</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>117.4194771985163</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1212449845413926</v>
+      </c>
+      <c r="C13">
+        <v>60.42550085220903</v>
+      </c>
+      <c r="D13">
+        <v>52.86260085220903</v>
+      </c>
+      <c r="E13">
+        <v>2.7271</v>
+      </c>
+      <c r="F13">
+        <v>7.4371</v>
+      </c>
+      <c r="G13">
+        <v>15</v>
+      </c>
+      <c r="H13">
+        <v>62.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>45.5</v>
+      </c>
+      <c r="K13">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L13">
+        <v>36.28</v>
+      </c>
+      <c r="M13">
+        <v>0.33987547</v>
+      </c>
+      <c r="N13">
+        <v>35.94012453</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>35.94012453</v>
+      </c>
+      <c r="Q13">
+        <v>45.16012453</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1305820051026884</v>
+      </c>
+      <c r="T13">
+        <v>1.320829219646363</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0.0457</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>106.7449792713784</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1213139845413926</v>
+      </c>
+      <c r="C14">
+        <v>59.74033960514895</v>
+      </c>
+      <c r="D14">
+        <v>52.85353960514895</v>
+      </c>
+      <c r="E14">
+        <v>3.403199999999999</v>
+      </c>
+      <c r="F14">
+        <v>8.113199999999999</v>
+      </c>
+      <c r="G14">
+        <v>15</v>
+      </c>
+      <c r="H14">
+        <v>62.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>45.5</v>
+      </c>
+      <c r="K14">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L14">
+        <v>36.28</v>
+      </c>
+      <c r="M14">
+        <v>0.37077324</v>
+      </c>
+      <c r="N14">
+        <v>35.90922676</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>35.90922676</v>
+      </c>
+      <c r="Q14">
+        <v>45.12922676</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1316249824334007</v>
+      </c>
+      <c r="T14">
+        <v>1.33583864259689</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0.0457</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>97.8495643320969</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1213829845413926</v>
+      </c>
+      <c r="C15">
+        <v>59.05518146395676</v>
+      </c>
+      <c r="D15">
+        <v>52.84448146395675</v>
+      </c>
+      <c r="E15">
+        <v>4.079300000000001</v>
+      </c>
+      <c r="F15">
+        <v>8.789300000000001</v>
+      </c>
+      <c r="G15">
+        <v>15</v>
+      </c>
+      <c r="H15">
+        <v>62.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>45.5</v>
+      </c>
+      <c r="K15">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L15">
+        <v>36.28</v>
+      </c>
+      <c r="M15">
+        <v>0.4016710100000001</v>
+      </c>
+      <c r="N15">
+        <v>35.87832899</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>35.87832899</v>
+      </c>
+      <c r="Q15">
+        <v>45.09832899</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1326919362544743</v>
+      </c>
+      <c r="T15">
+        <v>1.351193109753176</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0.0457</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>90.32267476808943</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1214519845413926</v>
+      </c>
+      <c r="C16">
+        <v>58.37002642703582</v>
+      </c>
+      <c r="D16">
+        <v>52.83542642703583</v>
+      </c>
+      <c r="E16">
+        <v>4.755400000000001</v>
+      </c>
+      <c r="F16">
+        <v>9.465400000000001</v>
+      </c>
+      <c r="G16">
+        <v>15</v>
+      </c>
+      <c r="H16">
+        <v>62.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>45.5</v>
+      </c>
+      <c r="K16">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L16">
+        <v>36.28</v>
+      </c>
+      <c r="M16">
+        <v>0.4325687800000001</v>
+      </c>
+      <c r="N16">
+        <v>35.84743122</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>35.84743122</v>
+      </c>
+      <c r="Q16">
+        <v>45.06743122</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1337837029551077</v>
+      </c>
+      <c r="T16">
+        <v>1.366904657541004</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0.0457</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>83.87105514179733</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1215209845413927</v>
+      </c>
+      <c r="C17">
+        <v>57.68487449279068</v>
+      </c>
+      <c r="D17">
+        <v>52.82637449279067</v>
+      </c>
+      <c r="E17">
+        <v>5.431499999999999</v>
+      </c>
+      <c r="F17">
+        <v>10.1415</v>
+      </c>
+      <c r="G17">
+        <v>15</v>
+      </c>
+      <c r="H17">
+        <v>62.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>45.5</v>
+      </c>
+      <c r="K17">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L17">
+        <v>36.28</v>
+      </c>
+      <c r="M17">
+        <v>0.46346655</v>
+      </c>
+      <c r="N17">
+        <v>35.81653345</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>35.81653345</v>
+      </c>
+      <c r="Q17">
+        <v>45.03653345</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1349011582839914</v>
+      </c>
+      <c r="T17">
+        <v>1.382985888806192</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0.0457</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>78.27965146567752</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1215899845413926</v>
+      </c>
+      <c r="C18">
+        <v>56.9997256596269</v>
+      </c>
+      <c r="D18">
+        <v>52.8173256596269</v>
+      </c>
+      <c r="E18">
+        <v>6.107600000000001</v>
+      </c>
+      <c r="F18">
+        <v>10.8176</v>
+      </c>
+      <c r="G18">
+        <v>15</v>
+      </c>
+      <c r="H18">
+        <v>62.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>45.5</v>
+      </c>
+      <c r="K18">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L18">
+        <v>36.28</v>
+      </c>
+      <c r="M18">
+        <v>0.4943643200000001</v>
+      </c>
+      <c r="N18">
+        <v>35.78563568</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>35.78563568</v>
+      </c>
+      <c r="Q18">
+        <v>45.00563568</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1360452196921341</v>
+      </c>
+      <c r="T18">
+        <v>1.399450006530075</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0.0457</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>73.38717324907266</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1216589845413926</v>
+      </c>
+      <c r="C19">
+        <v>56.31457992595115</v>
+      </c>
+      <c r="D19">
+        <v>52.80827992595116</v>
+      </c>
+      <c r="E19">
+        <v>6.783700000000001</v>
+      </c>
+      <c r="F19">
+        <v>11.4937</v>
+      </c>
+      <c r="G19">
+        <v>15</v>
+      </c>
+      <c r="H19">
+        <v>62.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>45.5</v>
+      </c>
+      <c r="K19">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L19">
+        <v>36.28</v>
+      </c>
+      <c r="M19">
+        <v>0.5252620900000001</v>
+      </c>
+      <c r="N19">
+        <v>35.75473791</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>35.75473791</v>
+      </c>
+      <c r="Q19">
+        <v>44.97473791</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1372168488450514</v>
+      </c>
+      <c r="T19">
+        <v>1.416310849982245</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0.0457</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>69.07028070500957</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1217279845413926</v>
+      </c>
+      <c r="C20">
+        <v>55.62943729017125</v>
+      </c>
+      <c r="D20">
+        <v>52.79923729017126</v>
+      </c>
+      <c r="E20">
+        <v>7.459799999999999</v>
+      </c>
+      <c r="F20">
+        <v>12.1698</v>
+      </c>
+      <c r="G20">
+        <v>15</v>
+      </c>
+      <c r="H20">
+        <v>62.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>45.5</v>
+      </c>
+      <c r="K20">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L20">
+        <v>36.28</v>
+      </c>
+      <c r="M20">
+        <v>0.55615986</v>
+      </c>
+      <c r="N20">
+        <v>35.72384014</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>35.72384014</v>
+      </c>
+      <c r="Q20">
+        <v>44.94384014</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1384170543187715</v>
+      </c>
+      <c r="T20">
+        <v>1.433582933518613</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0.0457</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>65.2330428880646</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1217969845413926</v>
+      </c>
+      <c r="C21">
+        <v>54.94429775069604</v>
+      </c>
+      <c r="D21">
+        <v>52.79019775069604</v>
+      </c>
+      <c r="E21">
+        <v>8.135899999999999</v>
+      </c>
+      <c r="F21">
+        <v>12.8459</v>
+      </c>
+      <c r="G21">
+        <v>15</v>
+      </c>
+      <c r="H21">
+        <v>62.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>45.5</v>
+      </c>
+      <c r="K21">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L21">
+        <v>36.28</v>
+      </c>
+      <c r="M21">
+        <v>0.5870576300000001</v>
+      </c>
+      <c r="N21">
+        <v>35.69294237</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>35.69294237</v>
+      </c>
+      <c r="Q21">
+        <v>44.91294237</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1396468944955465</v>
+      </c>
+      <c r="T21">
+        <v>1.451281488253411</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0.0457</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>61.79972484132435</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1218659845413926</v>
+      </c>
+      <c r="C22">
+        <v>54.25916130593547</v>
+      </c>
+      <c r="D22">
+        <v>52.78116130593547</v>
+      </c>
+      <c r="E22">
+        <v>8.812000000000001</v>
+      </c>
+      <c r="F22">
+        <v>13.522</v>
+      </c>
+      <c r="G22">
+        <v>15</v>
+      </c>
+      <c r="H22">
+        <v>62.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>45.5</v>
+      </c>
+      <c r="K22">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L22">
+        <v>36.28</v>
+      </c>
+      <c r="M22">
+        <v>0.6179554</v>
+      </c>
+      <c r="N22">
+        <v>35.6620446</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>35.6620446</v>
+      </c>
+      <c r="Q22">
+        <v>44.8820446</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1409074806767408</v>
+      </c>
+      <c r="T22">
+        <v>1.469422506856579</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0.0457</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>58.70973859925813</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1219349845413926</v>
+      </c>
+      <c r="C23">
+        <v>53.5740279543006</v>
+      </c>
+      <c r="D23">
+        <v>52.77212795430059</v>
+      </c>
+      <c r="E23">
+        <v>9.488099999999999</v>
+      </c>
+      <c r="F23">
+        <v>14.1981</v>
+      </c>
+      <c r="G23">
+        <v>15</v>
+      </c>
+      <c r="H23">
+        <v>62.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>45.5</v>
+      </c>
+      <c r="K23">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L23">
+        <v>36.28</v>
+      </c>
+      <c r="M23">
+        <v>0.6488531700000001</v>
+      </c>
+      <c r="N23">
+        <v>35.63114683</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>35.63114683</v>
+      </c>
+      <c r="Q23">
+        <v>44.85114683</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1421999804321426</v>
+      </c>
+      <c r="T23">
+        <v>1.488022791753498</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0.0457</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>55.91403676119821</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1220039845413926</v>
+      </c>
+      <c r="C24">
+        <v>52.88889769420354</v>
+      </c>
+      <c r="D24">
+        <v>52.76309769420354</v>
+      </c>
+      <c r="E24">
+        <v>10.1642</v>
+      </c>
+      <c r="F24">
+        <v>14.8742</v>
+      </c>
+      <c r="G24">
+        <v>15</v>
+      </c>
+      <c r="H24">
+        <v>62.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>45.5</v>
+      </c>
+      <c r="K24">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L24">
+        <v>36.28</v>
+      </c>
+      <c r="M24">
+        <v>0.67975094</v>
+      </c>
+      <c r="N24">
+        <v>35.60024906</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>35.60024906</v>
+      </c>
+      <c r="Q24">
+        <v>44.82024906</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1435256212069136</v>
+      </c>
+      <c r="T24">
+        <v>1.507100007032389</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0.0457</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>53.37248963568921</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1220729845413927</v>
+      </c>
+      <c r="C25">
+        <v>52.20377052405754</v>
+      </c>
+      <c r="D25">
+        <v>52.75407052405754</v>
+      </c>
+      <c r="E25">
+        <v>10.8403</v>
+      </c>
+      <c r="F25">
+        <v>15.5503</v>
+      </c>
+      <c r="G25">
+        <v>15</v>
+      </c>
+      <c r="H25">
+        <v>62.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>45.5</v>
+      </c>
+      <c r="K25">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L25">
+        <v>36.28</v>
+      </c>
+      <c r="M25">
+        <v>0.7106487100000001</v>
+      </c>
+      <c r="N25">
+        <v>35.56935129</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>35.56935129</v>
+      </c>
+      <c r="Q25">
+        <v>44.78935129</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1448856942096008</v>
+      </c>
+      <c r="T25">
+        <v>1.526672734396446</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0.0457</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>51.05194660805055</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1221419845413927</v>
+      </c>
+      <c r="C26">
+        <v>51.51864644227688</v>
+      </c>
+      <c r="D26">
+        <v>52.74504644227687</v>
+      </c>
+      <c r="E26">
+        <v>11.5164</v>
+      </c>
+      <c r="F26">
+        <v>16.2264</v>
+      </c>
+      <c r="G26">
+        <v>15</v>
+      </c>
+      <c r="H26">
+        <v>62.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>45.5</v>
+      </c>
+      <c r="K26">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L26">
+        <v>36.28</v>
+      </c>
+      <c r="M26">
+        <v>0.74154648</v>
+      </c>
+      <c r="N26">
+        <v>35.53845352</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>35.53845352</v>
+      </c>
+      <c r="Q26">
+        <v>44.75845352</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1462815586070956</v>
+      </c>
+      <c r="T26">
+        <v>1.546760533533241</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0.0457</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>48.92478216604845</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1222109845413926</v>
+      </c>
+      <c r="C27">
+        <v>50.83352544727694</v>
+      </c>
+      <c r="D27">
+        <v>52.73602544727694</v>
+      </c>
+      <c r="E27">
+        <v>12.1925</v>
+      </c>
+      <c r="F27">
+        <v>16.9025</v>
+      </c>
+      <c r="G27">
+        <v>15</v>
+      </c>
+      <c r="H27">
+        <v>62.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>45.5</v>
+      </c>
+      <c r="K27">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L27">
+        <v>36.28</v>
+      </c>
+      <c r="M27">
+        <v>0.7724442500000001</v>
+      </c>
+      <c r="N27">
+        <v>35.50755575</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>35.50755575</v>
+      </c>
+      <c r="Q27">
+        <v>44.72755575</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1477146460551902</v>
+      </c>
+      <c r="T27">
+        <v>1.567384007313684</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0.0457</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>46.96779087940651</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1222799845413926</v>
+      </c>
+      <c r="C28">
+        <v>50.14840753747423</v>
+      </c>
+      <c r="D28">
+        <v>52.72700753747423</v>
+      </c>
+      <c r="E28">
+        <v>12.8686</v>
+      </c>
+      <c r="F28">
+        <v>17.5786</v>
+      </c>
+      <c r="G28">
+        <v>15</v>
+      </c>
+      <c r="H28">
+        <v>62.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>45.5</v>
+      </c>
+      <c r="K28">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L28">
+        <v>36.28</v>
+      </c>
+      <c r="M28">
+        <v>0.8033420200000001</v>
+      </c>
+      <c r="N28">
+        <v>35.47665798</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>35.47665798</v>
+      </c>
+      <c r="Q28">
+        <v>44.69665798</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1491864655964766</v>
+      </c>
+      <c r="T28">
+        <v>1.588564872277383</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0.0457</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>45.16133738404471</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1223489845413927</v>
+      </c>
+      <c r="C29">
+        <v>49.46329271128627</v>
+      </c>
+      <c r="D29">
+        <v>52.71799271128627</v>
+      </c>
+      <c r="E29">
+        <v>13.5447</v>
+      </c>
+      <c r="F29">
+        <v>18.2547</v>
+      </c>
+      <c r="G29">
+        <v>15</v>
+      </c>
+      <c r="H29">
+        <v>62.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>45.5</v>
+      </c>
+      <c r="K29">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L29">
+        <v>36.28</v>
+      </c>
+      <c r="M29">
+        <v>0.83423979</v>
+      </c>
+      <c r="N29">
+        <v>35.44576021</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>35.44576021</v>
+      </c>
+      <c r="Q29">
+        <v>44.66576021</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1506986089608119</v>
+      </c>
+      <c r="T29">
+        <v>1.61032603491132</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0.0457</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>43.48869525870973</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1224179845413927</v>
+      </c>
+      <c r="C30">
+        <v>48.7781809671317</v>
+      </c>
+      <c r="D30">
+        <v>52.70898096713172</v>
+      </c>
+      <c r="E30">
+        <v>14.2208</v>
+      </c>
+      <c r="F30">
+        <v>18.9308</v>
+      </c>
+      <c r="G30">
+        <v>15</v>
+      </c>
+      <c r="H30">
+        <v>62.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>45.5</v>
+      </c>
+      <c r="K30">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L30">
+        <v>36.28</v>
+      </c>
+      <c r="M30">
+        <v>0.8651375600000002</v>
+      </c>
+      <c r="N30">
+        <v>35.41486244</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>35.41486244</v>
+      </c>
+      <c r="Q30">
+        <v>44.63486244</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1522527563074898</v>
+      </c>
+      <c r="T30">
+        <v>1.632691674285088</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0.0457</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>41.93552757089866</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1224869845413926</v>
+      </c>
+      <c r="C31">
+        <v>48.09307230343029</v>
+      </c>
+      <c r="D31">
+        <v>52.69997230343029</v>
+      </c>
+      <c r="E31">
+        <v>14.8969</v>
+      </c>
+      <c r="F31">
+        <v>19.6069</v>
+      </c>
+      <c r="G31">
+        <v>15</v>
+      </c>
+      <c r="H31">
+        <v>62.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>45.5</v>
+      </c>
+      <c r="K31">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L31">
+        <v>36.28</v>
+      </c>
+      <c r="M31">
+        <v>0.89603533</v>
+      </c>
+      <c r="N31">
+        <v>35.38396467</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>35.38396467</v>
+      </c>
+      <c r="Q31">
+        <v>44.60396467</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1538506824526657</v>
+      </c>
+      <c r="T31">
+        <v>1.655687331669385</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0.0457</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>40.4894748960401</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1225559845413926</v>
+      </c>
+      <c r="C32">
+        <v>47.40796671860278</v>
+      </c>
+      <c r="D32">
+        <v>52.69096671860278</v>
+      </c>
+      <c r="E32">
+        <v>15.573</v>
+      </c>
+      <c r="F32">
+        <v>20.283</v>
+      </c>
+      <c r="G32">
+        <v>15</v>
+      </c>
+      <c r="H32">
+        <v>62.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>45.5</v>
+      </c>
+      <c r="K32">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L32">
+        <v>36.28</v>
+      </c>
+      <c r="M32">
+        <v>0.9269331</v>
+      </c>
+      <c r="N32">
+        <v>35.3530669</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>35.3530669</v>
+      </c>
+      <c r="Q32">
+        <v>44.5730669</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1554942636305609</v>
+      </c>
+      <c r="T32">
+        <v>1.67934000783609</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0.0457</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>39.13982573283876</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1226249845413926</v>
+      </c>
+      <c r="C33">
+        <v>46.72286421107106</v>
+      </c>
+      <c r="D33">
+        <v>52.68196421107106</v>
+      </c>
+      <c r="E33">
+        <v>16.2491</v>
+      </c>
+      <c r="F33">
+        <v>20.9591</v>
+      </c>
+      <c r="G33">
+        <v>15</v>
+      </c>
+      <c r="H33">
+        <v>62.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>45.5</v>
+      </c>
+      <c r="K33">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L33">
+        <v>36.28</v>
+      </c>
+      <c r="M33">
+        <v>0.9578308700000001</v>
+      </c>
+      <c r="N33">
+        <v>35.32216913</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>35.32216913</v>
+      </c>
+      <c r="Q33">
+        <v>44.54216913</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.157185484842598</v>
+      </c>
+      <c r="T33">
+        <v>1.703678268819222</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0.0457</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>37.87725070919879</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1226939845413927</v>
+      </c>
+      <c r="C34">
+        <v>46.03776477925811</v>
+      </c>
+      <c r="D34">
+        <v>52.6729647792581</v>
+      </c>
+      <c r="E34">
+        <v>16.9252</v>
+      </c>
+      <c r="F34">
+        <v>21.6352</v>
+      </c>
+      <c r="G34">
+        <v>15</v>
+      </c>
+      <c r="H34">
+        <v>62.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>45.5</v>
+      </c>
+      <c r="K34">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L34">
+        <v>36.28</v>
+      </c>
+      <c r="M34">
+        <v>0.9887286400000002</v>
+      </c>
+      <c r="N34">
+        <v>35.29127136</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>35.29127136</v>
+      </c>
+      <c r="Q34">
+        <v>44.51127136</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1589264478549892</v>
+      </c>
+      <c r="T34">
+        <v>1.72873236100774</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0.0457</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>36.69358662453633</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1227629845413926</v>
+      </c>
+      <c r="C35">
+        <v>45.35266842158792</v>
+      </c>
+      <c r="D35">
+        <v>52.66396842158793</v>
+      </c>
+      <c r="E35">
+        <v>17.6013</v>
+      </c>
+      <c r="F35">
+        <v>22.3113</v>
+      </c>
+      <c r="G35">
+        <v>15</v>
+      </c>
+      <c r="H35">
+        <v>62.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>45.5</v>
+      </c>
+      <c r="K35">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L35">
+        <v>36.28</v>
+      </c>
+      <c r="M35">
+        <v>1.01962641</v>
+      </c>
+      <c r="N35">
+        <v>35.26037359</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>35.26037359</v>
+      </c>
+      <c r="Q35">
+        <v>44.48037359</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1607193799125263</v>
+      </c>
+      <c r="T35">
+        <v>1.754534336545169</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0.0457</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>35.58165975712614</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1228319845413926</v>
+      </c>
+      <c r="C36">
+        <v>44.66757513648566</v>
+      </c>
+      <c r="D36">
+        <v>52.65497513648566</v>
+      </c>
+      <c r="E36">
+        <v>18.2774</v>
+      </c>
+      <c r="F36">
+        <v>22.9874</v>
+      </c>
+      <c r="G36">
+        <v>15</v>
+      </c>
+      <c r="H36">
+        <v>62.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>45.5</v>
+      </c>
+      <c r="K36">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L36">
+        <v>36.28</v>
+      </c>
+      <c r="M36">
+        <v>1.05052418</v>
+      </c>
+      <c r="N36">
+        <v>35.22947582</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>35.22947582</v>
+      </c>
+      <c r="Q36">
+        <v>44.44947582</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1625666432445343</v>
+      </c>
+      <c r="T36">
+        <v>1.781118190129187</v>
+      </c>
+      <c r="U36">
+        <v>0.0457</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0.0457</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>34.53514035250478</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1229009845413926</v>
+      </c>
+      <c r="C37">
+        <v>43.98248492237748</v>
+      </c>
+      <c r="D37">
+        <v>52.64598492237748</v>
+      </c>
+      <c r="E37">
+        <v>18.9535</v>
+      </c>
+      <c r="F37">
+        <v>23.6635</v>
+      </c>
+      <c r="G37">
+        <v>15</v>
+      </c>
+      <c r="H37">
+        <v>62.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>45.5</v>
+      </c>
+      <c r="K37">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L37">
+        <v>36.28</v>
+      </c>
+      <c r="M37">
+        <v>1.08142195</v>
+      </c>
+      <c r="N37">
+        <v>35.19857805</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>35.19857805</v>
+      </c>
+      <c r="Q37">
+        <v>44.41857805</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1644707454482964</v>
+      </c>
+      <c r="T37">
+        <v>1.808520008438866</v>
+      </c>
+      <c r="U37">
+        <v>0.0457</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0.0457</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>33.54842205671893</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1229699845413927</v>
+      </c>
+      <c r="C38">
+        <v>43.29739777769064</v>
+      </c>
+      <c r="D38">
+        <v>52.63699777769064</v>
+      </c>
+      <c r="E38">
+        <v>19.6296</v>
+      </c>
+      <c r="F38">
+        <v>24.3396</v>
+      </c>
+      <c r="G38">
+        <v>15</v>
+      </c>
+      <c r="H38">
+        <v>62.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>45.5</v>
+      </c>
+      <c r="K38">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L38">
+        <v>36.28</v>
+      </c>
+      <c r="M38">
+        <v>1.11231972</v>
+      </c>
+      <c r="N38">
+        <v>35.16768028</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>35.16768028</v>
+      </c>
+      <c r="Q38">
+        <v>44.38768028</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.166434350845926</v>
+      </c>
+      <c r="T38">
+        <v>1.836778133570724</v>
+      </c>
+      <c r="U38">
+        <v>0.0457</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0.0457</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>32.6165214440323</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1230389845413926</v>
+      </c>
+      <c r="C39">
+        <v>42.61231370085348</v>
+      </c>
+      <c r="D39">
+        <v>52.62801370085348</v>
+      </c>
+      <c r="E39">
+        <v>20.3057</v>
+      </c>
+      <c r="F39">
+        <v>25.0157</v>
+      </c>
+      <c r="G39">
+        <v>15</v>
+      </c>
+      <c r="H39">
+        <v>62.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>45.5</v>
+      </c>
+      <c r="K39">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L39">
+        <v>36.28</v>
+      </c>
+      <c r="M39">
+        <v>1.14321749</v>
+      </c>
+      <c r="N39">
+        <v>35.13678251</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>35.13678251</v>
+      </c>
+      <c r="Q39">
+        <v>44.35678251</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1684602929228455</v>
+      </c>
+      <c r="T39">
+        <v>1.8659333420401</v>
+      </c>
+      <c r="U39">
+        <v>0.0457</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0.0457</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>31.73499383743683</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1231079845413926</v>
+      </c>
+      <c r="C40">
+        <v>41.9272326902954</v>
+      </c>
+      <c r="D40">
+        <v>52.61903269029541</v>
+      </c>
+      <c r="E40">
+        <v>20.9818</v>
+      </c>
+      <c r="F40">
+        <v>25.6918</v>
+      </c>
+      <c r="G40">
+        <v>15</v>
+      </c>
+      <c r="H40">
+        <v>62.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>45.5</v>
+      </c>
+      <c r="K40">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L40">
+        <v>36.28</v>
+      </c>
+      <c r="M40">
+        <v>1.17411526</v>
+      </c>
+      <c r="N40">
+        <v>35.10588474</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>35.10588474</v>
+      </c>
+      <c r="Q40">
+        <v>44.32588474</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1705515879699881</v>
+      </c>
+      <c r="T40">
+        <v>1.896029041105263</v>
+      </c>
+      <c r="U40">
+        <v>0.0457</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0.0457</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>30.89986242066217</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1231769845413926</v>
+      </c>
+      <c r="C41">
+        <v>41.24215474444689</v>
+      </c>
+      <c r="D41">
+        <v>52.6100547444469</v>
+      </c>
+      <c r="E41">
+        <v>21.6579</v>
+      </c>
+      <c r="F41">
+        <v>26.3679</v>
+      </c>
+      <c r="G41">
+        <v>15</v>
+      </c>
+      <c r="H41">
+        <v>62.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>45.5</v>
+      </c>
+      <c r="K41">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L41">
+        <v>36.28</v>
+      </c>
+      <c r="M41">
+        <v>1.20501303</v>
+      </c>
+      <c r="N41">
+        <v>35.07498697</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>35.07498697</v>
+      </c>
+      <c r="Q41">
+        <v>44.29498697</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1727114500678568</v>
+      </c>
+      <c r="T41">
+        <v>1.927111484402071</v>
+      </c>
+      <c r="U41">
+        <v>0.0457</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0.0457</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>30.10755825602981</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1232459845413927</v>
+      </c>
+      <c r="C42">
+        <v>40.55707986173952</v>
+      </c>
+      <c r="D42">
+        <v>52.60107986173951</v>
+      </c>
+      <c r="E42">
+        <v>22.334</v>
+      </c>
+      <c r="F42">
+        <v>27.044</v>
+      </c>
+      <c r="G42">
+        <v>15</v>
+      </c>
+      <c r="H42">
+        <v>62.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>45.5</v>
+      </c>
+      <c r="K42">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L42">
+        <v>36.28</v>
+      </c>
+      <c r="M42">
+        <v>1.2359108</v>
+      </c>
+      <c r="N42">
+        <v>35.0440892</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>35.0440892</v>
+      </c>
+      <c r="Q42">
+        <v>44.2640892</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1749433075689878</v>
+      </c>
+      <c r="T42">
+        <v>1.959230009142105</v>
+      </c>
+      <c r="U42">
+        <v>0.0457</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0.0457</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>29.35486929962907</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1233149845413926</v>
+      </c>
+      <c r="C43">
+        <v>39.87200804060586</v>
+      </c>
+      <c r="D43">
+        <v>52.59210804060586</v>
+      </c>
+      <c r="E43">
+        <v>23.0101</v>
+      </c>
+      <c r="F43">
+        <v>27.7201</v>
+      </c>
+      <c r="G43">
+        <v>15</v>
+      </c>
+      <c r="H43">
+        <v>62.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>45.5</v>
+      </c>
+      <c r="K43">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L43">
+        <v>36.28</v>
+      </c>
+      <c r="M43">
+        <v>1.26680857</v>
+      </c>
+      <c r="N43">
+        <v>35.01319143</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>35.01319143</v>
+      </c>
+      <c r="Q43">
+        <v>44.23319143</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1772508212565977</v>
+      </c>
+      <c r="T43">
+        <v>1.992437297432649</v>
+      </c>
+      <c r="U43">
+        <v>0.0457</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0.0457</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>28.63889687768689</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1233839845413927</v>
+      </c>
+      <c r="C44">
+        <v>39.18693927947964</v>
+      </c>
+      <c r="D44">
+        <v>52.58313927947965</v>
+      </c>
+      <c r="E44">
+        <v>23.6862</v>
+      </c>
+      <c r="F44">
+        <v>28.3962</v>
+      </c>
+      <c r="G44">
+        <v>15</v>
+      </c>
+      <c r="H44">
+        <v>62.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>45.5</v>
+      </c>
+      <c r="K44">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L44">
+        <v>36.28</v>
+      </c>
+      <c r="M44">
+        <v>1.29770634</v>
+      </c>
+      <c r="N44">
+        <v>34.98229366</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>34.98229366</v>
+      </c>
+      <c r="Q44">
+        <v>44.20229366</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1796379043817115</v>
+      </c>
+      <c r="T44">
+        <v>2.026789664629764</v>
+      </c>
+      <c r="U44">
+        <v>0.0457</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0.0457</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>27.95701838059911</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1234529845413927</v>
+      </c>
+      <c r="C45">
+        <v>38.5018735767956</v>
+      </c>
+      <c r="D45">
+        <v>52.57417357679561</v>
+      </c>
+      <c r="E45">
+        <v>24.3623</v>
+      </c>
+      <c r="F45">
+        <v>29.0723</v>
+      </c>
+      <c r="G45">
+        <v>15</v>
+      </c>
+      <c r="H45">
+        <v>62.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>45.5</v>
+      </c>
+      <c r="K45">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L45">
+        <v>36.28</v>
+      </c>
+      <c r="M45">
+        <v>1.32860411</v>
+      </c>
+      <c r="N45">
+        <v>34.95139589</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>34.95139589</v>
+      </c>
+      <c r="Q45">
+        <v>44.17139589</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1821087448094608</v>
+      </c>
+      <c r="T45">
+        <v>2.062347378044321</v>
+      </c>
+      <c r="U45">
+        <v>0.0457</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0.0457</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>27.30685516244564</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1235219845413926</v>
+      </c>
+      <c r="C46">
+        <v>37.81681093098958</v>
+      </c>
+      <c r="D46">
+        <v>52.56521093098958</v>
+      </c>
+      <c r="E46">
+        <v>25.0384</v>
+      </c>
+      <c r="F46">
+        <v>29.7484</v>
+      </c>
+      <c r="G46">
+        <v>15</v>
+      </c>
+      <c r="H46">
+        <v>62.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>45.5</v>
+      </c>
+      <c r="K46">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L46">
+        <v>36.28</v>
+      </c>
+      <c r="M46">
+        <v>1.35950188</v>
+      </c>
+      <c r="N46">
+        <v>34.92049812</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>34.92049812</v>
+      </c>
+      <c r="Q46">
+        <v>44.14049812</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1846678295382011</v>
+      </c>
+      <c r="T46">
+        <v>2.099175009795113</v>
+      </c>
+      <c r="U46">
+        <v>0.0457</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0.0457</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>26.6862448178446</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1235909845413927</v>
+      </c>
+      <c r="C47">
+        <v>37.13175134049845</v>
+      </c>
+      <c r="D47">
+        <v>52.55625134049846</v>
+      </c>
+      <c r="E47">
+        <v>25.7145</v>
+      </c>
+      <c r="F47">
+        <v>30.4245</v>
+      </c>
+      <c r="G47">
+        <v>15</v>
+      </c>
+      <c r="H47">
+        <v>62.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>45.5</v>
+      </c>
+      <c r="K47">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L47">
+        <v>36.28</v>
+      </c>
+      <c r="M47">
+        <v>1.39039965</v>
+      </c>
+      <c r="N47">
+        <v>34.88960035</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>34.88960035</v>
+      </c>
+      <c r="Q47">
+        <v>44.10960035</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1873199718934412</v>
+      </c>
+      <c r="T47">
+        <v>2.137341828155024</v>
+      </c>
+      <c r="U47">
+        <v>0.0457</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0.0457</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>26.09321715522584</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1236599845413927</v>
+      </c>
+      <c r="C48">
+        <v>36.4466948037602</v>
+      </c>
+      <c r="D48">
+        <v>52.5472948037602</v>
+      </c>
+      <c r="E48">
+        <v>26.3906</v>
+      </c>
+      <c r="F48">
+        <v>31.1006</v>
+      </c>
+      <c r="G48">
+        <v>15</v>
+      </c>
+      <c r="H48">
+        <v>62.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>45.5</v>
+      </c>
+      <c r="K48">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L48">
+        <v>36.28</v>
+      </c>
+      <c r="M48">
+        <v>1.42129742</v>
+      </c>
+      <c r="N48">
+        <v>34.85870258</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>34.85870258</v>
+      </c>
+      <c r="Q48">
+        <v>44.07870258</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1900703417433197</v>
+      </c>
+      <c r="T48">
+        <v>2.176922232380117</v>
+      </c>
+      <c r="U48">
+        <v>0.0457</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0.0457</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>25.52597330402527</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1237289845413927</v>
+      </c>
+      <c r="C49">
+        <v>35.76164131921379</v>
+      </c>
+      <c r="D49">
+        <v>52.53834131921381</v>
+      </c>
+      <c r="E49">
+        <v>27.0667</v>
+      </c>
+      <c r="F49">
+        <v>31.7767</v>
+      </c>
+      <c r="G49">
+        <v>15</v>
+      </c>
+      <c r="H49">
+        <v>62.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>45.5</v>
+      </c>
+      <c r="K49">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L49">
+        <v>36.28</v>
+      </c>
+      <c r="M49">
+        <v>1.45219519</v>
+      </c>
+      <c r="N49">
+        <v>34.82780481</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>34.82780481</v>
+      </c>
+      <c r="Q49">
+        <v>44.04780481</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1929244991347031</v>
+      </c>
+      <c r="T49">
+        <v>2.217996236764647</v>
+      </c>
+      <c r="U49">
+        <v>0.0457</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0.0457</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>24.98286748904601</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1237979845413926</v>
+      </c>
+      <c r="C50">
+        <v>35.0765908852994</v>
+      </c>
+      <c r="D50">
+        <v>52.52939088529939</v>
+      </c>
+      <c r="E50">
+        <v>27.7428</v>
+      </c>
+      <c r="F50">
+        <v>32.4528</v>
+      </c>
+      <c r="G50">
+        <v>15</v>
+      </c>
+      <c r="H50">
+        <v>62.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>45.5</v>
+      </c>
+      <c r="K50">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L50">
+        <v>36.28</v>
+      </c>
+      <c r="M50">
+        <v>1.48309296</v>
+      </c>
+      <c r="N50">
+        <v>34.79690704</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>34.79690704</v>
+      </c>
+      <c r="Q50">
+        <v>44.01690704</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1958884318103704</v>
+      </c>
+      <c r="T50">
+        <v>2.260650010548583</v>
+      </c>
+      <c r="U50">
+        <v>0.0457</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0.0457</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>24.46239108302422</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1238669845413926</v>
+      </c>
+      <c r="C51">
+        <v>34.39154350045808</v>
+      </c>
+      <c r="D51">
+        <v>52.52044350045809</v>
+      </c>
+      <c r="E51">
+        <v>28.4189</v>
+      </c>
+      <c r="F51">
+        <v>33.1289</v>
+      </c>
+      <c r="G51">
+        <v>15</v>
+      </c>
+      <c r="H51">
+        <v>62.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>45.5</v>
+      </c>
+      <c r="K51">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L51">
+        <v>36.28</v>
+      </c>
+      <c r="M51">
+        <v>1.51399073</v>
+      </c>
+      <c r="N51">
+        <v>34.76600927</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>34.76600927</v>
+      </c>
+      <c r="Q51">
+        <v>43.98600927</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1989685971399855</v>
+      </c>
+      <c r="T51">
+        <v>2.304976481343653</v>
+      </c>
+      <c r="U51">
+        <v>0.0457</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0.0457</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>23.96315861194209</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1239359845413927</v>
+      </c>
+      <c r="C52">
+        <v>33.7064991631321</v>
+      </c>
+      <c r="D52">
+        <v>52.51149916313211</v>
+      </c>
+      <c r="E52">
+        <v>29.095</v>
+      </c>
+      <c r="F52">
+        <v>33.805</v>
+      </c>
+      <c r="G52">
+        <v>15</v>
+      </c>
+      <c r="H52">
+        <v>62.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>45.5</v>
+      </c>
+      <c r="K52">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L52">
+        <v>36.28</v>
+      </c>
+      <c r="M52">
+        <v>1.5448885</v>
+      </c>
+      <c r="N52">
+        <v>34.7351115</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>34.7351115</v>
+      </c>
+      <c r="Q52">
+        <v>43.9551115</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2021719690827853</v>
+      </c>
+      <c r="T52">
+        <v>2.351076010970526</v>
+      </c>
+      <c r="U52">
+        <v>0.0457</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0.0457</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>23.48389543970325</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1240049845413926</v>
+      </c>
+      <c r="C53">
+        <v>33.02145787176474</v>
+      </c>
+      <c r="D53">
+        <v>52.50255787176473</v>
+      </c>
+      <c r="E53">
+        <v>29.7711</v>
+      </c>
+      <c r="F53">
+        <v>34.4811</v>
+      </c>
+      <c r="G53">
+        <v>15</v>
+      </c>
+      <c r="H53">
+        <v>62.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>45.5</v>
+      </c>
+      <c r="K53">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L53">
+        <v>36.28</v>
+      </c>
+      <c r="M53">
+        <v>1.57578627</v>
+      </c>
+      <c r="N53">
+        <v>34.70421373</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>34.70421373</v>
+      </c>
+      <c r="Q53">
+        <v>43.92421373</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2055060909008013</v>
+      </c>
+      <c r="T53">
+        <v>2.399057154051557</v>
+      </c>
+      <c r="U53">
+        <v>0.0457</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0.0457</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>23.02342690166985</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1240739845413927</v>
+      </c>
+      <c r="C54">
+        <v>32.33641962480026</v>
+      </c>
+      <c r="D54">
+        <v>52.49361962480027</v>
+      </c>
+      <c r="E54">
+        <v>30.4472</v>
+      </c>
+      <c r="F54">
+        <v>35.1572</v>
+      </c>
+      <c r="G54">
+        <v>15</v>
+      </c>
+      <c r="H54">
+        <v>62.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>45.5</v>
+      </c>
+      <c r="K54">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L54">
+        <v>36.28</v>
+      </c>
+      <c r="M54">
+        <v>1.60668404</v>
+      </c>
+      <c r="N54">
+        <v>34.67331596</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>34.67331596</v>
+      </c>
+      <c r="Q54">
+        <v>43.89331596</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2089791344612347</v>
+      </c>
+      <c r="T54">
+        <v>2.449037511427631</v>
+      </c>
+      <c r="U54">
+        <v>0.0457</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0.0457</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>22.58066869202236</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1241429845413927</v>
+      </c>
+      <c r="C55">
+        <v>31.65138442068412</v>
+      </c>
+      <c r="D55">
+        <v>52.48468442068413</v>
+      </c>
+      <c r="E55">
+        <v>31.1233</v>
+      </c>
+      <c r="F55">
+        <v>35.8333</v>
+      </c>
+      <c r="G55">
+        <v>15</v>
+      </c>
+      <c r="H55">
+        <v>62.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>45.5</v>
+      </c>
+      <c r="K55">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L55">
+        <v>36.28</v>
+      </c>
+      <c r="M55">
+        <v>1.63758181</v>
+      </c>
+      <c r="N55">
+        <v>34.64241819</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>34.64241819</v>
+      </c>
+      <c r="Q55">
+        <v>43.86241819</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2125999671093461</v>
+      </c>
+      <c r="T55">
+        <v>2.501144692521836</v>
+      </c>
+      <c r="U55">
+        <v>0.0457</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0.0457</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>22.15461833934269</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1242119845413926</v>
+      </c>
+      <c r="C56">
+        <v>30.96635225786275</v>
+      </c>
+      <c r="D56">
+        <v>52.47575225786275</v>
+      </c>
+      <c r="E56">
+        <v>31.7994</v>
+      </c>
+      <c r="F56">
+        <v>36.5094</v>
+      </c>
+      <c r="G56">
+        <v>15</v>
+      </c>
+      <c r="H56">
+        <v>62.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>45.5</v>
+      </c>
+      <c r="K56">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L56">
+        <v>36.28</v>
+      </c>
+      <c r="M56">
+        <v>1.66847958</v>
+      </c>
+      <c r="N56">
+        <v>34.61152042</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>34.61152042</v>
+      </c>
+      <c r="Q56">
+        <v>43.83152042</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.216378227263897</v>
+      </c>
+      <c r="T56">
+        <v>2.555517403228833</v>
+      </c>
+      <c r="U56">
+        <v>0.0457</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0.0457</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>21.74434762935486</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1242809845413927</v>
+      </c>
+      <c r="C57">
+        <v>30.28132313478365</v>
+      </c>
+      <c r="D57">
+        <v>52.46682313478365</v>
+      </c>
+      <c r="E57">
+        <v>32.4755</v>
+      </c>
+      <c r="F57">
+        <v>37.1855</v>
+      </c>
+      <c r="G57">
+        <v>15</v>
+      </c>
+      <c r="H57">
+        <v>62.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>45.5</v>
+      </c>
+      <c r="K57">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L57">
+        <v>36.28</v>
+      </c>
+      <c r="M57">
+        <v>1.69937735</v>
+      </c>
+      <c r="N57">
+        <v>34.58062265</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>34.58062265</v>
+      </c>
+      <c r="Q57">
+        <v>43.80062265</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2203244100919837</v>
+      </c>
+      <c r="T57">
+        <v>2.61230667885614</v>
+      </c>
+      <c r="U57">
+        <v>0.0457</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0.0457</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>21.34899585427568</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1243499845413926</v>
+      </c>
+      <c r="C58">
+        <v>29.59629704989538</v>
+      </c>
+      <c r="D58">
+        <v>52.45789704989538</v>
+      </c>
+      <c r="E58">
+        <v>33.1516</v>
+      </c>
+      <c r="F58">
+        <v>37.8616</v>
+      </c>
+      <c r="G58">
+        <v>15</v>
+      </c>
+      <c r="H58">
+        <v>62.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>45.5</v>
+      </c>
+      <c r="K58">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L58">
+        <v>36.28</v>
+      </c>
+      <c r="M58">
+        <v>1.73027512</v>
+      </c>
+      <c r="N58">
+        <v>34.54972488</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>34.54972488</v>
+      </c>
+      <c r="Q58">
+        <v>43.76972488</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2244499648668015</v>
+      </c>
+      <c r="T58">
+        <v>2.67167728519378</v>
+      </c>
+      <c r="U58">
+        <v>0.0457</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0.0457</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>20.96776378544933</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1244189845413926</v>
+      </c>
+      <c r="C59">
+        <v>28.91127400164757</v>
+      </c>
+      <c r="D59">
+        <v>52.44897400164757</v>
+      </c>
+      <c r="E59">
+        <v>33.8277</v>
+      </c>
+      <c r="F59">
+        <v>38.5377</v>
+      </c>
+      <c r="G59">
+        <v>15</v>
+      </c>
+      <c r="H59">
+        <v>62.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>45.5</v>
+      </c>
+      <c r="K59">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L59">
+        <v>36.28</v>
+      </c>
+      <c r="M59">
+        <v>1.76117289</v>
+      </c>
+      <c r="N59">
+        <v>34.51882711</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>34.51882711</v>
+      </c>
+      <c r="Q59">
+        <v>43.73882711</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2287674059102155</v>
+      </c>
+      <c r="T59">
+        <v>2.733809315082008</v>
+      </c>
+      <c r="U59">
+        <v>0.0457</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0.0457</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>20.59990828044145</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1244879845413926</v>
+      </c>
+      <c r="C60">
+        <v>28.22625398849089</v>
+      </c>
+      <c r="D60">
+        <v>52.44005398849088</v>
+      </c>
+      <c r="E60">
+        <v>34.5038</v>
+      </c>
+      <c r="F60">
+        <v>39.2138</v>
+      </c>
+      <c r="G60">
+        <v>15</v>
+      </c>
+      <c r="H60">
+        <v>62.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>45.5</v>
+      </c>
+      <c r="K60">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L60">
+        <v>36.28</v>
+      </c>
+      <c r="M60">
+        <v>1.79207066</v>
+      </c>
+      <c r="N60">
+        <v>34.48792934</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>34.48792934</v>
+      </c>
+      <c r="Q60">
+        <v>43.70792934</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2332904393842682</v>
+      </c>
+      <c r="T60">
+        <v>2.79890001306015</v>
+      </c>
+      <c r="U60">
+        <v>0.0457</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0.0457</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>20.24473744802005</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1245569845413926</v>
+      </c>
+      <c r="C61">
+        <v>27.54123700887705</v>
+      </c>
+      <c r="D61">
+        <v>52.43113700887704</v>
+      </c>
+      <c r="E61">
+        <v>35.1799</v>
+      </c>
+      <c r="F61">
+        <v>39.8899</v>
+      </c>
+      <c r="G61">
+        <v>15</v>
+      </c>
+      <c r="H61">
+        <v>62.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>45.5</v>
+      </c>
+      <c r="K61">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L61">
+        <v>36.28</v>
+      </c>
+      <c r="M61">
+        <v>1.82296843</v>
+      </c>
+      <c r="N61">
+        <v>34.45703157</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>34.45703157</v>
+      </c>
+      <c r="Q61">
+        <v>43.67703157</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.238034108637543</v>
+      </c>
+      <c r="T61">
+        <v>2.867165867037226</v>
+      </c>
+      <c r="U61">
+        <v>0.0457</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0.0457</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>19.90160630483327</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1246259845413926</v>
+      </c>
+      <c r="C62">
+        <v>26.85622306125885</v>
+      </c>
+      <c r="D62">
+        <v>52.42222306125884</v>
+      </c>
+      <c r="E62">
+        <v>35.85599999999999</v>
+      </c>
+      <c r="F62">
+        <v>40.566</v>
+      </c>
+      <c r="G62">
+        <v>15</v>
+      </c>
+      <c r="H62">
+        <v>62.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>45.5</v>
+      </c>
+      <c r="K62">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L62">
+        <v>36.28</v>
+      </c>
+      <c r="M62">
+        <v>1.8538662</v>
+      </c>
+      <c r="N62">
+        <v>34.4261338</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>34.4261338</v>
+      </c>
+      <c r="Q62">
+        <v>43.6461338</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2430149613534816</v>
+      </c>
+      <c r="T62">
+        <v>2.938845013713158</v>
+      </c>
+      <c r="U62">
+        <v>0.0457</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0.0457</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>19.56991286641938</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1246949845413926</v>
+      </c>
+      <c r="C63">
+        <v>26.1712121440901</v>
+      </c>
+      <c r="D63">
+        <v>52.41331214409009</v>
+      </c>
+      <c r="E63">
+        <v>36.5321</v>
+      </c>
+      <c r="F63">
+        <v>41.2421</v>
+      </c>
+      <c r="G63">
+        <v>15</v>
+      </c>
+      <c r="H63">
+        <v>62.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>45.5</v>
+      </c>
+      <c r="K63">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L63">
+        <v>36.28</v>
+      </c>
+      <c r="M63">
+        <v>1.88476397</v>
+      </c>
+      <c r="N63">
+        <v>34.39523603</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>34.39523603</v>
+      </c>
+      <c r="Q63">
+        <v>43.61523603</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2482512424138273</v>
+      </c>
+      <c r="T63">
+        <v>3.014200014064777</v>
+      </c>
+      <c r="U63">
+        <v>0.0457</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0.0457</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>19.24909462270758</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1247639845413927</v>
+      </c>
+      <c r="C64">
+        <v>25.4862042558257</v>
+      </c>
+      <c r="D64">
+        <v>52.4044042558257</v>
+      </c>
+      <c r="E64">
+        <v>37.2082</v>
+      </c>
+      <c r="F64">
+        <v>41.9182</v>
+      </c>
+      <c r="G64">
+        <v>15</v>
+      </c>
+      <c r="H64">
+        <v>62.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>45.5</v>
+      </c>
+      <c r="K64">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L64">
+        <v>36.28</v>
+      </c>
+      <c r="M64">
+        <v>1.91566174</v>
+      </c>
+      <c r="N64">
+        <v>34.36433826</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>34.36433826</v>
+      </c>
+      <c r="Q64">
+        <v>43.58433826</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2537631172141912</v>
+      </c>
+      <c r="T64">
+        <v>3.093521067066482</v>
+      </c>
+      <c r="U64">
+        <v>0.0457</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0.0457</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>18.9386253545994</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1248329845413927</v>
+      </c>
+      <c r="C65">
+        <v>24.80119939492159</v>
+      </c>
+      <c r="D65">
+        <v>52.39549939492158</v>
+      </c>
+      <c r="E65">
+        <v>37.8843</v>
+      </c>
+      <c r="F65">
+        <v>42.5943</v>
+      </c>
+      <c r="G65">
+        <v>15</v>
+      </c>
+      <c r="H65">
+        <v>62.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>45.5</v>
+      </c>
+      <c r="K65">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L65">
+        <v>36.28</v>
+      </c>
+      <c r="M65">
+        <v>1.94655951</v>
+      </c>
+      <c r="N65">
+        <v>34.33344049</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>34.33344049</v>
+      </c>
+      <c r="Q65">
+        <v>43.55344049</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2595729311929531</v>
+      </c>
+      <c r="T65">
+        <v>3.177129744554765</v>
+      </c>
+      <c r="U65">
+        <v>0.0457</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0.0457</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>18.63801225373274</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1249019845413926</v>
+      </c>
+      <c r="C66">
+        <v>24.11619755983472</v>
+      </c>
+      <c r="D66">
+        <v>52.38659755983473</v>
+      </c>
+      <c r="E66">
+        <v>38.5604</v>
+      </c>
+      <c r="F66">
+        <v>43.2704</v>
+      </c>
+      <c r="G66">
+        <v>15</v>
+      </c>
+      <c r="H66">
+        <v>62.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>45.5</v>
+      </c>
+      <c r="K66">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L66">
+        <v>36.28</v>
+      </c>
+      <c r="M66">
+        <v>1.97745728</v>
+      </c>
+      <c r="N66">
+        <v>34.30254272</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>34.30254272</v>
+      </c>
+      <c r="Q66">
+        <v>43.52254272</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2657055126149795</v>
+      </c>
+      <c r="T66">
+        <v>3.265383348570175</v>
+      </c>
+      <c r="U66">
+        <v>0.0457</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0.0457</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>18.34679331226816</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1249709845413927</v>
+      </c>
+      <c r="C67">
+        <v>23.43119874902315</v>
+      </c>
+      <c r="D67">
+        <v>52.37769874902316</v>
+      </c>
+      <c r="E67">
+        <v>39.2365</v>
+      </c>
+      <c r="F67">
+        <v>43.9465</v>
+      </c>
+      <c r="G67">
+        <v>15</v>
+      </c>
+      <c r="H67">
+        <v>62.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>45.5</v>
+      </c>
+      <c r="K67">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L67">
+        <v>36.28</v>
+      </c>
+      <c r="M67">
+        <v>2.00835505</v>
+      </c>
+      <c r="N67">
+        <v>34.27164495</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>34.27164495</v>
+      </c>
+      <c r="Q67">
+        <v>43.49164495</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2721885272611219</v>
+      </c>
+      <c r="T67">
+        <v>3.358680015672181</v>
+      </c>
+      <c r="U67">
+        <v>0.0457</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0.0457</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>18.06453495361789</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1250399845413926</v>
+      </c>
+      <c r="C68">
+        <v>22.74620296094597</v>
+      </c>
+      <c r="D68">
+        <v>52.36880296094597</v>
+      </c>
+      <c r="E68">
+        <v>39.9126</v>
+      </c>
+      <c r="F68">
+        <v>44.6226</v>
+      </c>
+      <c r="G68">
+        <v>15</v>
+      </c>
+      <c r="H68">
+        <v>62.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>45.5</v>
+      </c>
+      <c r="K68">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L68">
+        <v>36.28</v>
+      </c>
+      <c r="M68">
+        <v>2.03925282</v>
+      </c>
+      <c r="N68">
+        <v>34.24074718</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>34.24074718</v>
+      </c>
+      <c r="Q68">
+        <v>43.46074718</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2790528957099784</v>
+      </c>
+      <c r="T68">
+        <v>3.45746472201548</v>
+      </c>
+      <c r="U68">
+        <v>0.0457</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0.0457</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>17.79082987856307</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1251089845413926</v>
+      </c>
+      <c r="C69">
+        <v>22.06121019406327</v>
+      </c>
+      <c r="D69">
+        <v>52.35991019406327</v>
+      </c>
+      <c r="E69">
+        <v>40.5887</v>
+      </c>
+      <c r="F69">
+        <v>45.2987</v>
+      </c>
+      <c r="G69">
+        <v>15</v>
+      </c>
+      <c r="H69">
+        <v>62.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>45.5</v>
+      </c>
+      <c r="K69">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L69">
+        <v>36.28</v>
+      </c>
+      <c r="M69">
+        <v>2.07015059</v>
+      </c>
+      <c r="N69">
+        <v>34.20984941</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>34.20984941</v>
+      </c>
+      <c r="Q69">
+        <v>43.42984941</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2863332864890686</v>
+      </c>
+      <c r="T69">
+        <v>3.562236380258374</v>
+      </c>
+      <c r="U69">
+        <v>0.0457</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0.0457</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>17.52529510425616</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1251779845413927</v>
+      </c>
+      <c r="C70">
+        <v>21.37622044683623</v>
+      </c>
+      <c r="D70">
+        <v>52.35102044683623</v>
+      </c>
+      <c r="E70">
+        <v>41.2648</v>
+      </c>
+      <c r="F70">
+        <v>45.9748</v>
+      </c>
+      <c r="G70">
+        <v>15</v>
+      </c>
+      <c r="H70">
+        <v>62.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>45.5</v>
+      </c>
+      <c r="K70">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L70">
+        <v>36.28</v>
+      </c>
+      <c r="M70">
+        <v>2.101048360000001</v>
+      </c>
+      <c r="N70">
+        <v>34.17895164</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>34.17895164</v>
+      </c>
+      <c r="Q70">
+        <v>43.39895164</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2940687016918521</v>
+      </c>
+      <c r="T70">
+        <v>3.673556267141448</v>
+      </c>
+      <c r="U70">
+        <v>0.0457</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0.0457</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>17.26757017625239</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1252469845413927</v>
+      </c>
+      <c r="C71">
+        <v>20.69123371772708</v>
+      </c>
+      <c r="D71">
+        <v>52.34213371772709</v>
+      </c>
+      <c r="E71">
+        <v>41.9409</v>
+      </c>
+      <c r="F71">
+        <v>46.6509</v>
+      </c>
+      <c r="G71">
+        <v>15</v>
+      </c>
+      <c r="H71">
+        <v>62.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>45.5</v>
+      </c>
+      <c r="K71">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L71">
+        <v>36.28</v>
+      </c>
+      <c r="M71">
+        <v>2.13194613</v>
+      </c>
+      <c r="N71">
+        <v>34.14805387</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>34.14805387</v>
+      </c>
+      <c r="Q71">
+        <v>43.36805387</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3023031759399763</v>
+      </c>
+      <c r="T71">
+        <v>3.792058082210527</v>
+      </c>
+      <c r="U71">
+        <v>0.0457</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0.0457</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>17.01731553601685</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1253159845413926</v>
+      </c>
+      <c r="C72">
+        <v>20.00625000519906</v>
+      </c>
+      <c r="D72">
+        <v>52.33325000519907</v>
+      </c>
+      <c r="E72">
+        <v>42.617</v>
+      </c>
+      <c r="F72">
+        <v>47.32700000000001</v>
+      </c>
+      <c r="G72">
+        <v>15</v>
+      </c>
+      <c r="H72">
+        <v>62.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>45.5</v>
+      </c>
+      <c r="K72">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L72">
+        <v>36.28</v>
+      </c>
+      <c r="M72">
+        <v>2.1628439</v>
+      </c>
+      <c r="N72">
+        <v>34.1171561</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>34.1171561</v>
+      </c>
+      <c r="Q72">
+        <v>43.3371561</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3110866151379755</v>
+      </c>
+      <c r="T72">
+        <v>3.918460018284211</v>
+      </c>
+      <c r="U72">
+        <v>0.0457</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0.0457</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>16.77421102835947</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1253849845413927</v>
+      </c>
+      <c r="C73">
+        <v>19.3212693077165</v>
+      </c>
+      <c r="D73">
+        <v>52.3243693077165</v>
+      </c>
+      <c r="E73">
+        <v>43.2931</v>
+      </c>
+      <c r="F73">
+        <v>48.0031</v>
+      </c>
+      <c r="G73">
+        <v>15</v>
+      </c>
+      <c r="H73">
+        <v>62.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>45.5</v>
+      </c>
+      <c r="K73">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L73">
+        <v>36.28</v>
+      </c>
+      <c r="M73">
+        <v>2.19374167</v>
+      </c>
+      <c r="N73">
+        <v>34.08625833</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>34.08625833</v>
+      </c>
+      <c r="Q73">
+        <v>43.30625833</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3204758087634229</v>
+      </c>
+      <c r="T73">
+        <v>4.053579329259528</v>
+      </c>
+      <c r="U73">
+        <v>0.0457</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0.0457</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>16.53795453500229</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1254539845413926</v>
+      </c>
+      <c r="C74">
+        <v>18.63629162374473</v>
+      </c>
+      <c r="D74">
+        <v>52.31549162374473</v>
+      </c>
+      <c r="E74">
+        <v>43.96919999999999</v>
+      </c>
+      <c r="F74">
+        <v>48.67919999999999</v>
+      </c>
+      <c r="G74">
+        <v>15</v>
+      </c>
+      <c r="H74">
+        <v>62.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>45.5</v>
+      </c>
+      <c r="K74">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L74">
+        <v>36.28</v>
+      </c>
+      <c r="M74">
+        <v>2.22463944</v>
+      </c>
+      <c r="N74">
+        <v>34.05536056</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>34.05536056</v>
+      </c>
+      <c r="Q74">
+        <v>43.27536056</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3305356590764023</v>
+      </c>
+      <c r="T74">
+        <v>4.198350019590225</v>
+      </c>
+      <c r="U74">
+        <v>0.0457</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0.0457</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>16.30826072201615</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1255229845413927</v>
+      </c>
+      <c r="C75">
+        <v>17.95131695175012</v>
+      </c>
+      <c r="D75">
+        <v>52.30661695175012</v>
+      </c>
+      <c r="E75">
+        <v>44.6453</v>
+      </c>
+      <c r="F75">
+        <v>49.3553</v>
+      </c>
+      <c r="G75">
+        <v>15</v>
+      </c>
+      <c r="H75">
+        <v>62.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>45.5</v>
+      </c>
+      <c r="K75">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L75">
+        <v>36.28</v>
+      </c>
+      <c r="M75">
+        <v>2.25553721</v>
+      </c>
+      <c r="N75">
+        <v>34.02446279</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>34.02446279</v>
+      </c>
+      <c r="Q75">
+        <v>43.24446279</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3413406834866394</v>
+      </c>
+      <c r="T75">
+        <v>4.353844464760233</v>
+      </c>
+      <c r="U75">
+        <v>0.0457</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0.0457</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>16.08485989020771</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1255919845413926</v>
+      </c>
+      <c r="C76">
+        <v>17.26634529020011</v>
+      </c>
+      <c r="D76">
+        <v>52.29774529020012</v>
+      </c>
+      <c r="E76">
+        <v>45.3214</v>
+      </c>
+      <c r="F76">
+        <v>50.0314</v>
+      </c>
+      <c r="G76">
+        <v>15</v>
+      </c>
+      <c r="H76">
+        <v>62.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>45.5</v>
+      </c>
+      <c r="K76">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L76">
+        <v>36.28</v>
+      </c>
+      <c r="M76">
+        <v>2.28643498</v>
+      </c>
+      <c r="N76">
+        <v>33.99356502</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>33.99356502</v>
+      </c>
+      <c r="Q76">
+        <v>43.21356502</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3529768636207409</v>
+      </c>
+      <c r="T76">
+        <v>4.521300021097165</v>
+      </c>
+      <c r="U76">
+        <v>0.0457</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0.0457</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>15.86749691871841</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1256609845413926</v>
+      </c>
+      <c r="C77">
+        <v>16.5813766375632</v>
+      </c>
+      <c r="D77">
+        <v>52.28887663756318</v>
+      </c>
+      <c r="E77">
+        <v>45.9975</v>
+      </c>
+      <c r="F77">
+        <v>50.7075</v>
+      </c>
+      <c r="G77">
+        <v>15</v>
+      </c>
+      <c r="H77">
+        <v>62.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>45.5</v>
+      </c>
+      <c r="K77">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L77">
+        <v>36.28</v>
+      </c>
+      <c r="M77">
+        <v>2.31733275</v>
+      </c>
+      <c r="N77">
+        <v>33.96266725</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>33.96266725</v>
+      </c>
+      <c r="Q77">
+        <v>43.18266725</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3655439381655706</v>
+      </c>
+      <c r="T77">
+        <v>4.702152021941052</v>
+      </c>
+      <c r="U77">
+        <v>0.0457</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0.0457</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>15.6559302931355</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1257299845413926</v>
+      </c>
+      <c r="C78">
+        <v>15.89641099230882</v>
+      </c>
+      <c r="D78">
+        <v>52.28001099230882</v>
+      </c>
+      <c r="E78">
+        <v>46.6736</v>
+      </c>
+      <c r="F78">
+        <v>51.3836</v>
+      </c>
+      <c r="G78">
+        <v>15</v>
+      </c>
+      <c r="H78">
+        <v>62.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>45.5</v>
+      </c>
+      <c r="K78">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L78">
+        <v>36.28</v>
+      </c>
+      <c r="M78">
+        <v>2.34823052</v>
+      </c>
+      <c r="N78">
+        <v>33.93176948</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>33.93176948</v>
+      </c>
+      <c r="Q78">
+        <v>43.15176948</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3791582689224693</v>
+      </c>
+      <c r="T78">
+        <v>4.898075022855263</v>
+      </c>
+      <c r="U78">
+        <v>0.0457</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0.0457</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>15.44993121033109</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1257989845413926</v>
+      </c>
+      <c r="C79">
+        <v>15.21144835290757</v>
+      </c>
+      <c r="D79">
+        <v>52.27114835290757</v>
+      </c>
+      <c r="E79">
+        <v>47.3497</v>
+      </c>
+      <c r="F79">
+        <v>52.0597</v>
+      </c>
+      <c r="G79">
+        <v>15</v>
+      </c>
+      <c r="H79">
+        <v>62.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>45.5</v>
+      </c>
+      <c r="K79">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L79">
+        <v>36.28</v>
+      </c>
+      <c r="M79">
+        <v>2.37912829</v>
+      </c>
+      <c r="N79">
+        <v>33.90087171</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>33.90087171</v>
+      </c>
+      <c r="Q79">
+        <v>43.12087171</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3939564545277941</v>
+      </c>
+      <c r="T79">
+        <v>5.111034806457665</v>
+      </c>
+      <c r="U79">
+        <v>0.0457</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0.0457</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>15.24928275305406</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1258679845413926</v>
+      </c>
+      <c r="C80">
+        <v>14.52648871783101</v>
+      </c>
+      <c r="D80">
+        <v>52.26228871783101</v>
+      </c>
+      <c r="E80">
+        <v>48.0258</v>
+      </c>
+      <c r="F80">
+        <v>52.7358</v>
+      </c>
+      <c r="G80">
+        <v>15</v>
+      </c>
+      <c r="H80">
+        <v>62.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>45.5</v>
+      </c>
+      <c r="K80">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L80">
+        <v>36.28</v>
+      </c>
+      <c r="M80">
+        <v>2.41002606</v>
+      </c>
+      <c r="N80">
+        <v>33.86997394</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>33.86997394</v>
+      </c>
+      <c r="Q80">
+        <v>43.08997394</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.410099929733603</v>
+      </c>
+      <c r="T80">
+        <v>5.34335457038756</v>
+      </c>
+      <c r="U80">
+        <v>0.0457</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0.0457</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>15.05377912801491</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1259369845413927</v>
+      </c>
+      <c r="C81">
+        <v>13.84153208555176</v>
+      </c>
+      <c r="D81">
+        <v>52.25343208555177</v>
+      </c>
+      <c r="E81">
+        <v>48.7019</v>
+      </c>
+      <c r="F81">
+        <v>53.4119</v>
+      </c>
+      <c r="G81">
+        <v>15</v>
+      </c>
+      <c r="H81">
+        <v>62.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>45.5</v>
+      </c>
+      <c r="K81">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L81">
+        <v>36.28</v>
+      </c>
+      <c r="M81">
+        <v>2.44092383</v>
+      </c>
+      <c r="N81">
+        <v>33.83907617</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>33.83907617</v>
+      </c>
+      <c r="Q81">
+        <v>43.05907617</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4277808787685365</v>
+      </c>
+      <c r="T81">
+        <v>5.597800026120302</v>
+      </c>
+      <c r="U81">
+        <v>0.0457</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0.0457</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>14.8632249618375</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1260059845413926</v>
+      </c>
+      <c r="C82">
+        <v>13.15657845454349</v>
+      </c>
+      <c r="D82">
+        <v>52.24457845454349</v>
+      </c>
+      <c r="E82">
+        <v>49.378</v>
+      </c>
+      <c r="F82">
+        <v>54.088</v>
+      </c>
+      <c r="G82">
+        <v>15</v>
+      </c>
+      <c r="H82">
+        <v>62.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>45.5</v>
+      </c>
+      <c r="K82">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L82">
+        <v>36.28</v>
+      </c>
+      <c r="M82">
+        <v>2.4718216</v>
+      </c>
+      <c r="N82">
+        <v>33.8081784</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>33.8081784</v>
+      </c>
+      <c r="Q82">
+        <v>43.0281784</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4472299227069633</v>
+      </c>
+      <c r="T82">
+        <v>5.877690027426317</v>
+      </c>
+      <c r="U82">
+        <v>0.0457</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0.0457</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>14.67743464981453</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1260749845413927</v>
+      </c>
+      <c r="C83">
+        <v>12.47162782328085</v>
+      </c>
+      <c r="D83">
+        <v>52.23572782328085</v>
+      </c>
+      <c r="E83">
+        <v>50.05410000000001</v>
+      </c>
+      <c r="F83">
+        <v>54.76410000000001</v>
+      </c>
+      <c r="G83">
+        <v>15</v>
+      </c>
+      <c r="H83">
+        <v>62.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>45.5</v>
+      </c>
+      <c r="K83">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L83">
+        <v>36.28</v>
+      </c>
+      <c r="M83">
+        <v>2.50271937</v>
+      </c>
+      <c r="N83">
+        <v>33.77728063</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>33.77728063</v>
+      </c>
+      <c r="Q83">
+        <v>42.99728063</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4687262344283825</v>
+      </c>
+      <c r="T83">
+        <v>6.187042134132965</v>
+      </c>
+      <c r="U83">
+        <v>0.0457</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0.0457</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>14.49623175290324</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1261439845413926</v>
+      </c>
+      <c r="C84">
+        <v>11.78668019023958</v>
+      </c>
+      <c r="D84">
+        <v>52.22688019023958</v>
+      </c>
+      <c r="E84">
+        <v>50.7302</v>
+      </c>
+      <c r="F84">
+        <v>55.4402</v>
+      </c>
+      <c r="G84">
+        <v>15</v>
+      </c>
+      <c r="H84">
+        <v>62.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>45.5</v>
+      </c>
+      <c r="K84">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L84">
+        <v>36.28</v>
+      </c>
+      <c r="M84">
+        <v>2.53361714</v>
+      </c>
+      <c r="N84">
+        <v>33.74638286</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>33.74638286</v>
+      </c>
+      <c r="Q84">
+        <v>42.96638286</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4926110252299593</v>
+      </c>
+      <c r="T84">
+        <v>6.530766697140352</v>
+      </c>
+      <c r="U84">
+        <v>0.0457</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0.0457</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>14.31944843884344</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1262129845413926</v>
+      </c>
+      <c r="C85">
+        <v>11.10173555389644</v>
+      </c>
+      <c r="D85">
+        <v>52.21803555389643</v>
+      </c>
+      <c r="E85">
+        <v>51.4063</v>
+      </c>
+      <c r="F85">
+        <v>56.1163</v>
+      </c>
+      <c r="G85">
+        <v>15</v>
+      </c>
+      <c r="H85">
+        <v>62.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>45.5</v>
+      </c>
+      <c r="K85">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L85">
+        <v>36.28</v>
+      </c>
+      <c r="M85">
+        <v>2.56451491</v>
+      </c>
+      <c r="N85">
+        <v>33.71548509</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>33.71548509</v>
+      </c>
+      <c r="Q85">
+        <v>42.93548509</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5193057914199569</v>
+      </c>
+      <c r="T85">
+        <v>6.914929444030962</v>
+      </c>
+      <c r="U85">
+        <v>0.0457</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0.0457</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>14.14692496367666</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1262819845413927</v>
+      </c>
+      <c r="C86">
+        <v>10.41679391272918</v>
+      </c>
+      <c r="D86">
+        <v>52.20919391272917</v>
+      </c>
+      <c r="E86">
+        <v>52.0824</v>
+      </c>
+      <c r="F86">
+        <v>56.7924</v>
+      </c>
+      <c r="G86">
+        <v>15</v>
+      </c>
+      <c r="H86">
+        <v>62.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>45.5</v>
+      </c>
+      <c r="K86">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L86">
+        <v>36.28</v>
+      </c>
+      <c r="M86">
+        <v>2.59541268</v>
+      </c>
+      <c r="N86">
+        <v>33.68458732</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>33.68458732</v>
+      </c>
+      <c r="Q86">
+        <v>42.90458732</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.549337403383704</v>
+      </c>
+      <c r="T86">
+        <v>7.347112534282894</v>
+      </c>
+      <c r="U86">
+        <v>0.0457</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0.0457</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>13.97850919029955</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1263509845413927</v>
+      </c>
+      <c r="C87">
+        <v>9.731855265216645</v>
+      </c>
+      <c r="D87">
+        <v>52.20035526521664</v>
+      </c>
+      <c r="E87">
+        <v>52.7585</v>
+      </c>
+      <c r="F87">
+        <v>57.4685</v>
+      </c>
+      <c r="G87">
+        <v>15</v>
+      </c>
+      <c r="H87">
+        <v>62.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>45.5</v>
+      </c>
+      <c r="K87">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L87">
+        <v>36.28</v>
+      </c>
+      <c r="M87">
+        <v>2.62631045</v>
+      </c>
+      <c r="N87">
+        <v>33.65368955</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>33.65368955</v>
+      </c>
+      <c r="Q87">
+        <v>42.87368955</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5833732302759509</v>
+      </c>
+      <c r="T87">
+        <v>7.83692003656842</v>
+      </c>
+      <c r="U87">
+        <v>0.0457</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0.0457</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>13.81405614100191</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1264199845413926</v>
+      </c>
+      <c r="C88">
+        <v>9.046919609838653</v>
+      </c>
+      <c r="D88">
+        <v>52.19151960983864</v>
+      </c>
+      <c r="E88">
+        <v>53.4346</v>
+      </c>
+      <c r="F88">
+        <v>58.1446</v>
+      </c>
+      <c r="G88">
+        <v>15</v>
+      </c>
+      <c r="H88">
+        <v>62.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>45.5</v>
+      </c>
+      <c r="K88">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L88">
+        <v>36.28</v>
+      </c>
+      <c r="M88">
+        <v>2.65720822</v>
+      </c>
+      <c r="N88">
+        <v>33.62279178</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>33.62279178</v>
+      </c>
+      <c r="Q88">
+        <v>42.84279178</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6222713181528046</v>
+      </c>
+      <c r="T88">
+        <v>8.39670003918045</v>
+      </c>
+      <c r="U88">
+        <v>0.0457</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88">
+        <v>0.0457</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>13.65342758122282</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1264889845413926</v>
+      </c>
+      <c r="C89">
+        <v>8.361986945076083</v>
+      </c>
+      <c r="D89">
+        <v>52.18268694507609</v>
+      </c>
+      <c r="E89">
+        <v>54.1107</v>
+      </c>
+      <c r="F89">
+        <v>58.8207</v>
+      </c>
+      <c r="G89">
+        <v>15</v>
+      </c>
+      <c r="H89">
+        <v>62.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>45.5</v>
+      </c>
+      <c r="K89">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L89">
+        <v>36.28</v>
+      </c>
+      <c r="M89">
+        <v>2.68810599</v>
+      </c>
+      <c r="N89">
+        <v>33.59189401</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>33.59189401</v>
+      </c>
+      <c r="Q89">
+        <v>42.81189401</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6671537272414818</v>
+      </c>
+      <c r="T89">
+        <v>9.04260004219433</v>
+      </c>
+      <c r="U89">
+        <v>0.0457</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>0.0457</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>13.49649163201336</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1265579845413926</v>
+      </c>
+      <c r="C90">
+        <v>7.677057269410859</v>
+      </c>
+      <c r="D90">
+        <v>52.17385726941087</v>
+      </c>
+      <c r="E90">
+        <v>54.7868</v>
+      </c>
+      <c r="F90">
+        <v>59.4968</v>
+      </c>
+      <c r="G90">
+        <v>15</v>
+      </c>
+      <c r="H90">
+        <v>62.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>45.5</v>
+      </c>
+      <c r="K90">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L90">
+        <v>36.28</v>
+      </c>
+      <c r="M90">
+        <v>2.71900376</v>
+      </c>
+      <c r="N90">
+        <v>33.56099624</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>33.56099624</v>
+      </c>
+      <c r="Q90">
+        <v>42.78099624</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7195165378449386</v>
+      </c>
+      <c r="T90">
+        <v>9.796150045710526</v>
+      </c>
+      <c r="U90">
+        <v>0.0457</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>0.0457</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>13.3431224089223</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1266269845413927</v>
+      </c>
+      <c r="C91">
+        <v>6.99213058132591</v>
+      </c>
+      <c r="D91">
+        <v>52.1650305813259</v>
+      </c>
+      <c r="E91">
+        <v>55.4629</v>
+      </c>
+      <c r="F91">
+        <v>60.1729</v>
+      </c>
+      <c r="G91">
+        <v>15</v>
+      </c>
+      <c r="H91">
+        <v>62.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>45.5</v>
+      </c>
+      <c r="K91">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L91">
+        <v>36.28</v>
+      </c>
+      <c r="M91">
+        <v>2.74990153</v>
+      </c>
+      <c r="N91">
+        <v>33.53009847</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>33.53009847</v>
+      </c>
+      <c r="Q91">
+        <v>42.75009847</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.781399859467206</v>
+      </c>
+      <c r="T91">
+        <v>10.68670914077512</v>
+      </c>
+      <c r="U91">
+        <v>0.0457</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0.0457</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>13.19319968522655</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1266959845413926</v>
+      </c>
+      <c r="C92">
+        <v>6.307206879305141</v>
+      </c>
+      <c r="D92">
+        <v>52.15620687930515</v>
+      </c>
+      <c r="E92">
+        <v>56.139</v>
+      </c>
+      <c r="F92">
+        <v>60.849</v>
+      </c>
+      <c r="G92">
+        <v>15</v>
+      </c>
+      <c r="H92">
+        <v>62.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>45.5</v>
+      </c>
+      <c r="K92">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L92">
+        <v>36.28</v>
+      </c>
+      <c r="M92">
+        <v>2.7807993</v>
+      </c>
+      <c r="N92">
+        <v>33.4992007</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>33.4992007</v>
+      </c>
+      <c r="Q92">
+        <v>42.7192007</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8556598454139266</v>
+      </c>
+      <c r="T92">
+        <v>11.75538005485263</v>
+      </c>
+      <c r="U92">
+        <v>0.0457</v>
+      </c>
+      <c r="V92">
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <v>0.0457</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>13.04660857761292</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1282209845413926</v>
+      </c>
+      <c r="C93">
+        <v>5.43684948614294</v>
+      </c>
+      <c r="D93">
+        <v>51.96194948614294</v>
+      </c>
+      <c r="E93">
+        <v>56.8151</v>
+      </c>
+      <c r="F93">
+        <v>61.5251</v>
+      </c>
+      <c r="G93">
+        <v>15</v>
+      </c>
+      <c r="H93">
+        <v>62.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>45.5</v>
+      </c>
+      <c r="K93">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L93">
+        <v>36.28</v>
+      </c>
+      <c r="M93">
+        <v>2.91013723</v>
+      </c>
+      <c r="N93">
+        <v>33.36986277</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>33.36986277</v>
+      </c>
+      <c r="Q93">
+        <v>42.58986277</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.9464220504599186</v>
+      </c>
+      <c r="T93">
+        <v>13.0615333942807</v>
+      </c>
+      <c r="U93">
+        <v>0.0473</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <v>0.0473</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>12.46676604319446</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1283059845413927</v>
+      </c>
+      <c r="C94">
+        <v>4.749964591006091</v>
+      </c>
+      <c r="D94">
+        <v>51.9511645910061</v>
+      </c>
+      <c r="E94">
+        <v>57.4912</v>
+      </c>
+      <c r="F94">
+        <v>62.2012</v>
+      </c>
+      <c r="G94">
+        <v>15</v>
+      </c>
+      <c r="H94">
+        <v>62.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>45.5</v>
+      </c>
+      <c r="K94">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L94">
+        <v>36.28</v>
+      </c>
+      <c r="M94">
+        <v>2.94211676</v>
+      </c>
+      <c r="N94">
+        <v>33.33788324</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>33.33788324</v>
+      </c>
+      <c r="Q94">
+        <v>42.55788324</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.059874806767409</v>
+      </c>
+      <c r="T94">
+        <v>14.6942250685658</v>
+      </c>
+      <c r="U94">
+        <v>0.0473</v>
+      </c>
+      <c r="V94">
+        <v>0</v>
+      </c>
+      <c r="W94">
+        <v>0.0473</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>12.331257716638</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1283909845413927</v>
+      </c>
+      <c r="C95">
+        <v>4.063084171830141</v>
+      </c>
+      <c r="D95">
+        <v>51.94038417183015</v>
+      </c>
+      <c r="E95">
+        <v>58.1673</v>
+      </c>
+      <c r="F95">
+        <v>62.87730000000001</v>
+      </c>
+      <c r="G95">
+        <v>15</v>
+      </c>
+      <c r="H95">
+        <v>62.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>45.5</v>
+      </c>
+      <c r="K95">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L95">
+        <v>36.28</v>
+      </c>
+      <c r="M95">
+        <v>2.97409629</v>
+      </c>
+      <c r="N95">
+        <v>33.30590371</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>33.30590371</v>
+      </c>
+      <c r="Q95">
+        <v>42.52590371</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.20574263630561</v>
+      </c>
+      <c r="T95">
+        <v>16.79340007836091</v>
+      </c>
+      <c r="U95">
+        <v>0.0473</v>
+      </c>
+      <c r="V95">
+        <v>0</v>
+      </c>
+      <c r="W95">
+        <v>0.0473</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>12.1986635476419</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1284759845413926</v>
+      </c>
+      <c r="C96">
+        <v>3.376208225829224</v>
+      </c>
+      <c r="D96">
+        <v>51.92960822582923</v>
+      </c>
+      <c r="E96">
+        <v>58.8434</v>
+      </c>
+      <c r="F96">
+        <v>63.5534</v>
+      </c>
+      <c r="G96">
+        <v>15</v>
+      </c>
+      <c r="H96">
+        <v>62.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>45.5</v>
+      </c>
+      <c r="K96">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L96">
+        <v>36.28</v>
+      </c>
+      <c r="M96">
+        <v>3.00607582</v>
+      </c>
+      <c r="N96">
+        <v>33.27392418</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>33.27392418</v>
+      </c>
+      <c r="Q96">
+        <v>42.49392418</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.400233075689879</v>
+      </c>
+      <c r="T96">
+        <v>19.59230009142107</v>
+      </c>
+      <c r="U96">
+        <v>0.0473</v>
+      </c>
+      <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="W96">
+        <v>0.0473</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>12.06889053117762</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1285609845413926</v>
+      </c>
+      <c r="C97">
+        <v>2.689336750219809</v>
+      </c>
+      <c r="D97">
+        <v>51.91883675021981</v>
+      </c>
+      <c r="E97">
+        <v>59.5195</v>
+      </c>
+      <c r="F97">
+        <v>64.2295</v>
+      </c>
+      <c r="G97">
+        <v>15</v>
+      </c>
+      <c r="H97">
+        <v>62.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>45.5</v>
+      </c>
+      <c r="K97">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L97">
+        <v>36.28</v>
+      </c>
+      <c r="M97">
+        <v>3.03805535</v>
+      </c>
+      <c r="N97">
+        <v>33.24194465</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>33.24194465</v>
+      </c>
+      <c r="Q97">
+        <v>42.46194465</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.672519690827855</v>
+      </c>
+      <c r="T97">
+        <v>23.51076010970529</v>
+      </c>
+      <c r="U97">
+        <v>0.0473</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97">
+        <v>0.0473</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>11.94184957821786</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1286459845413926</v>
+      </c>
+      <c r="C98">
+        <v>2.002469742220654</v>
+      </c>
+      <c r="D98">
+        <v>51.90806974222065</v>
+      </c>
+      <c r="E98">
+        <v>60.19559999999999</v>
+      </c>
+      <c r="F98">
+        <v>64.90559999999999</v>
+      </c>
+      <c r="G98">
+        <v>15</v>
+      </c>
+      <c r="H98">
+        <v>62.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>45.5</v>
+      </c>
+      <c r="K98">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L98">
+        <v>36.28</v>
+      </c>
+      <c r="M98">
+        <v>3.07003488</v>
+      </c>
+      <c r="N98">
+        <v>33.20996512</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>33.20996512</v>
+      </c>
+      <c r="Q98">
+        <v>42.42996512</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.080949613534814</v>
+      </c>
+      <c r="T98">
+        <v>29.38845013713155</v>
+      </c>
+      <c r="U98">
+        <v>0.0473</v>
+      </c>
+      <c r="V98">
+        <v>0</v>
+      </c>
+      <c r="W98">
+        <v>0.0473</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>11.81745531177809</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1287309845413927</v>
+      </c>
+      <c r="C99">
+        <v>1.315607199052849</v>
+      </c>
+      <c r="D99">
+        <v>51.89730719905284</v>
+      </c>
+      <c r="E99">
+        <v>60.8717</v>
+      </c>
+      <c r="F99">
+        <v>65.5817</v>
+      </c>
+      <c r="G99">
+        <v>15</v>
+      </c>
+      <c r="H99">
+        <v>62.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>45.5</v>
+      </c>
+      <c r="K99">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L99">
+        <v>36.28</v>
+      </c>
+      <c r="M99">
+        <v>3.10201441</v>
+      </c>
+      <c r="N99">
+        <v>33.17798559</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>33.17798559</v>
+      </c>
+      <c r="Q99">
+        <v>42.39798559</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.761666151379753</v>
+      </c>
+      <c r="T99">
+        <v>39.18460018284208</v>
+      </c>
+      <c r="U99">
+        <v>0.0473</v>
+      </c>
+      <c r="V99">
+        <v>0</v>
+      </c>
+      <c r="W99">
+        <v>0.0473</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>11.69562587557419</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1288159845413926</v>
+      </c>
+      <c r="C100">
+        <v>0.6287491179397477</v>
+      </c>
+      <c r="D100">
+        <v>51.88654911793976</v>
+      </c>
+      <c r="E100">
+        <v>61.5478</v>
+      </c>
+      <c r="F100">
+        <v>66.2578</v>
+      </c>
+      <c r="G100">
+        <v>15</v>
+      </c>
+      <c r="H100">
+        <v>62.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>45.5</v>
+      </c>
+      <c r="K100">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L100">
+        <v>36.28</v>
+      </c>
+      <c r="M100">
+        <v>3.13399394</v>
+      </c>
+      <c r="N100">
+        <v>33.14600606</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>33.14600606</v>
+      </c>
+      <c r="Q100">
+        <v>42.36600606</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.123099227069629</v>
+      </c>
+      <c r="T100">
+        <v>58.77690027426311</v>
+      </c>
+      <c r="U100">
+        <v>0.0473</v>
+      </c>
+      <c r="V100">
+        <v>0</v>
+      </c>
+      <c r="W100">
+        <v>0.0473</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>11.57628275439486</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
         <v>0.99</v>
       </c>
-      <c r="AM3">
-        <v>0.969</v>
-      </c>
-      <c r="AN3">
-        <v>4.253968253968254</v>
-      </c>
-      <c r="AO3">
-        <v>-9.303030303030305</v>
-      </c>
-      <c r="AP3">
-        <v>4.058730158730159</v>
-      </c>
-      <c r="AQ3">
-        <v>-9.504643962848299</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cayman Islands</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Tethys Petroleum Limited (TSXV:TPL)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Oil/Gas (Production and Exploration)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>-0.0385</v>
-      </c>
-      <c r="G4">
-        <v>0.6345132743362831</v>
-      </c>
-      <c r="H4">
-        <v>0.6345132743362831</v>
-      </c>
-      <c r="I4">
-        <v>-3.486725663716814</v>
-      </c>
-      <c r="J4">
-        <v>-3.486725663716814</v>
-      </c>
-      <c r="K4">
-        <v>-35.7</v>
-      </c>
-      <c r="L4">
-        <v>-3.15929203539823</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0.658</v>
-      </c>
-      <c r="V4">
-        <v>0.01105882352941177</v>
-      </c>
-      <c r="W4">
-        <v>-0.6219512195121952</v>
-      </c>
-      <c r="X4">
-        <v>0.07658336099574439</v>
-      </c>
-      <c r="Y4">
-        <v>-0.6985345805079396</v>
-      </c>
-      <c r="Z4">
-        <v>0.181118769033499</v>
-      </c>
-      <c r="AA4">
-        <v>-0.631511460169899</v>
-      </c>
-      <c r="AB4">
-        <v>0.07480508053485013</v>
-      </c>
-      <c r="AC4">
-        <v>-0.7063165407047491</v>
-      </c>
-      <c r="AD4">
-        <v>6.3</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>6.3</v>
-      </c>
-      <c r="AG4">
-        <v>5.641999999999999</v>
-      </c>
-      <c r="AH4">
-        <v>0.09574468085106383</v>
-      </c>
-      <c r="AI4">
-        <v>0.1987381703470031</v>
-      </c>
-      <c r="AJ4">
-        <v>0.08661078873844831</v>
-      </c>
-      <c r="AK4">
-        <v>0.1817537529798338</v>
-      </c>
-      <c r="AL4">
-        <v>1.31</v>
-      </c>
-      <c r="AM4">
-        <v>1.187</v>
-      </c>
-      <c r="AN4">
-        <v>1.171003717472119</v>
-      </c>
-      <c r="AO4">
-        <v>-30.07633587786259</v>
-      </c>
-      <c r="AP4">
-        <v>1.048698884758364</v>
-      </c>
-      <c r="AQ4">
-        <v>-33.19292333614153</v>
+      <c r="B101">
+        <v>0.1289009845413926</v>
+      </c>
+      <c r="C101">
+        <v>-0.05810450389290622</v>
+      </c>
+      <c r="D101">
+        <v>51.87579549610708</v>
+      </c>
+      <c r="E101">
+        <v>62.22389999999999</v>
+      </c>
+      <c r="F101">
+        <v>66.93389999999999</v>
+      </c>
+      <c r="G101">
+        <v>15</v>
+      </c>
+      <c r="H101">
+        <v>62.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>45.5</v>
+      </c>
+      <c r="K101">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L101">
+        <v>36.28</v>
+      </c>
+      <c r="M101">
+        <v>3.16597347</v>
+      </c>
+      <c r="N101">
+        <v>33.11402653</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>33.11402653</v>
+      </c>
+      <c r="Q101">
+        <v>42.33402653</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>8.207398454139257</v>
+      </c>
+      <c r="T101">
+        <v>117.5538005485262</v>
+      </c>
+      <c r="U101">
+        <v>0.0473</v>
+      </c>
+      <c r="V101">
+        <v>0</v>
+      </c>
+      <c r="W101">
+        <v>0.0473</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>11.45935060536057</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
